--- a/LlmMoveiAgentResults.xlsx
+++ b/LlmMoveiAgentResults.xlsx
@@ -15,8 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -76,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -105,6 +106,7 @@
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -524,7 +526,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ42"/>
+  <dimension ref="A1:AJ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" style="7" min="1" max="1"/>
@@ -2262,7 +2264,7 @@
       </c>
       <c r="AJ15" s="8" t="inlineStr">
         <is>
-          <t>Verified, and worse than it looks — strict 3/42, answered 0 of 34. Made ZERO real tool calls in all 42 runs: it prints tool calls as prose ('&lt;|tool call{...}|&gt;' and json blocks) in 17 runs instead of using the tool-call channel. Re-ran with wire capture: 25 tool definitions were sent correctly and it described them accurately, then called none — model behaviour, not a harness fault. Its 4 'correct' include 2 grader false positives. Belongs with the hard fails.</t>
+          <t>HARD FAIL — zero tool calls in all 42 runs, wire-confirmed. Strict 3/42 and answered 0 of 34. It prints tool calls as prose ('&lt;|tool call{...}|&gt;' and json blocks) in 17 runs instead of using the tool-call channel. Re-ran with wire capture: 25 tool definitions were sent correctly and it described them accurately, then called none — model behaviour, not a harness fault. Its 4 'correct' include 2 grader false positives. The numbers here are real but should be read as a hard fail, not a low score.</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2386,7 @@
       </c>
       <c r="AJ16" s="8" t="inlineStr">
         <is>
-          <t>Verified. Strict 8/42 — but all 8 are refusals; it answered 0 of 34. Zero tool calls in all 42 runs and refuses 33 of 34 answerable questions ('I don't have access to information about...'). Wire capture confirms 25 tools were sent and none called. Its perfect 8/8 refusal score is the clearest demonstration here that refusal accuracy is meaningless without the over-refusal denominator. Belongs with the hard fails.</t>
+          <t>HARD FAIL — zero tool calls in all 42 runs, wire-confirmed (25 tools sent, none called). Strict 8/42, but all 8 are refusals; it answered 0 of 34 and refused 33 of 34 answerable questions ('I don't have access to information about...'). Its perfect 8/8 refusal score is the clearest demonstration here that refusal accuracy is meaningless without the over-refusal denominator.</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2869,129 @@
       </c>
       <c r="AJ20" s="8" t="inlineStr">
         <is>
-          <t>Verified. Strict 1/42. CORRECTION to an earlier note: that single point is NOT a truncation artefact — the run finished with finish_reason 'stop' and a complete sentence. It is a different false positive: the model narrates a plan it never executes ('I am calling search_films_by_title...') and the conditional phrase 'I cannot proceed further without guessing' trips the refusal classifier. Still unfixed. Ignored Agent:Thinking=false entirely (reasoning in 42/42 iterations) and burned the whole 2500-token cap in 31/42 runs, giving 31 empty answers and zero tool calls for the sweep. Mean 2298 output tokens vs ~100 elsewhere; 26 min wall clock. Untestable at this MaxOutputTokens rather than proven bad.</t>
+          <t>HARD FAIL — zero tool calls, wire-confirmed, at BOTH token caps. Strict 1/42 and its true score is 0: the single point is a grader artefact (a complete sentence containing the conditional 'I cannot proceed further without guessing', inside a plan it never executed, read as a refusal). RETEST: re-run at MaxOutputTokens 6000 (runs-20260813-162941.jsonl, 21 questions x 1 repeat) to test whether the 2500 cap was the cause. It was not. Truncation fell from 31/42 to 3/21 and empty answers from 31 to 3, so the cap was a real constraint — but tool calls stayed at ZERO and the score did not move. Every run is one iteration: no tool call means nothing to feed back. It writes an essay about calling tools instead (309,720 chars of reasoning vs 10,186 of answer) naming tools that mostly do not exist (search_film_by_title, get_rental_film_id). Wire at 6000: 25 tools sent, no tool_calls field, 11,497 chars of 'thinking', content ending '&lt;tool&gt;search_film_by_title&lt;/tool&gt;' — its own invented pseudo-syntax in the content channel. Also ignores Agent:Thinking=false entirely (reasoning in every iteration). Costs 50% more wall clock at the higher cap for an identical zero. The earlier 'untestable at this MaxOutputTokens' caveat is retired — the cap was hiding the failure, not causing it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>Phi4</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>Q4_K_M</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F21" s="16" t="n">
+        <v>45689</v>
+      </c>
+      <c r="G21" s="11" t="inlineStr">
+        <is>
+          <t>phi4-mini</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="11" t="inlineStr">
+        <is>
+          <t>runs-20260813-165949.jsonl</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="K21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="11" t="n">
+        <v>2289</v>
+      </c>
+      <c r="T21" s="11" t="n">
+        <v>113</v>
+      </c>
+      <c r="U21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="8" t="inlineStr">
+        <is>
+          <t>HARD FAIL — zero tool calls in all 21 runs, wire-confirmed. True score 0/21: the single 'correct' is the same planning-monologue false positive as deepseek-r1. NOTE THE DIFFERENT CONFIG: Repeats=1 (21 runs, not 42) and MaxOutputTokens 6000, so the counts here are not directly comparable with the rows above; the rates are. Distinct from the other zero-call failures and the closest call of the four: it emits STRUCTURALLY CORRECT tool-call JSON — [{"name": "get_film", "arguments": {"film_id": 1}}] — with real tool and parameter names, but into the content channel (15 of 21 runs). Checked properly because that shape suggests a rig fault: /api/show reports phi4-mini declares the 'tools' capability and its template does handle them, rendering tools into &lt;|tool|&gt;...&lt;|/tool|&gt; and expecting calls back wrapped as &lt;|tool_call|&gt;[...]&lt;|/tool_call|&gt;. Wire capture: 25 tools sent, no tool_calls field in the response, and the content carries the bare JSON array with NO &lt;|tool_call|&gt; delimiter. So the model omits the delimiter its own chat template requires and Ollama cannot parse the payload — a model failure, but one pair of tags away from working. Two aggravating factors: it also hallucinates the RESULTS, roleplaying whole conversations with invented rows (invents the city 'Springfield', invents actor ids [1,2,3] then concludes '3 actors'), and its text-format calls are frequently malformed anyway ({"arguments"} as a second object rather than a key; "parameters" instead of "arguments"). Invents tools that do not exist (search_rental, search_inventory_item). Fast and cheap at 113 output tokens and 2.0s per run, which buys nothing.</t>
         </is>
       </c>
     </row>
@@ -3815,48 +3939,80 @@
       </c>
     </row>
     <row r="36">
-      <c r="H36" s="11" t="n"/>
+      <c r="G36" s="11" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="H36" s="11" t="inlineStr">
+        <is>
+          <t>Retested at MaxOutputTokens 6000: still zero tool calls. Reclassified as a hard fail alongside granite3.3:8b and command-r7b — all wire-confirmed to receive 25 tool definitions and call none.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="G37" s="10" t="inlineStr">
+      <c r="G37" s="11" t="inlineStr">
+        <is>
+          <t>phi4-mini</t>
+        </is>
+      </c>
+      <c r="H37" s="11" t="inlineStr">
+        <is>
+          <t>Zero tool calls, but emits well-formed tool-call JSON into the content channel without the &lt;|tool_call|&gt; delimiter its own template requires. Run at Repeats=1 / cap 6000, so 21 runs not 42.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+    </row>
+    <row r="39">
+      <c r="G39" s="10" t="inlineStr">
         <is>
           <t>Validation</t>
         </is>
       </c>
-      <c r="H37" s="11" t="n"/>
-    </row>
-    <row r="38">
-      <c r="H38" s="11" t="inlineStr">
-        <is>
-          <t>All 22 rows recomputed from the regraded JSONL (grader deterministic-substring-v3). One transcription error found and corrected: ref /8 for qwen2.5:7b, 5 -&gt; 8.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="H39" s="11" t="inlineStr">
-        <is>
-          <t>v3 changes: fabricated arguments split into invented row id vs invented search term, and an answer truncated by the token cap can no longer be graded as a refusal. Regrading all 968 runs produced 0 correct/declined flips — both changes are additive.</t>
-        </is>
-      </c>
+      <c r="H39" s="11" t="n"/>
     </row>
     <row r="40">
       <c r="H40" s="11" t="inlineStr">
         <is>
-          <t>Caveat on the hop columns: the v2 near-miss and truncation questions all sit at hop 2, so 'hop 2 ans' measures search recovery as much as depth. Chain-only scores are in RESULTS-ANALYSIS.md.</t>
+          <t>All rows recomputed from the regraded JSONL (grader deterministic-substring-v3). One transcription error found and corrected: ref /8 for qwen2.5:7b, 5 -&gt; 8.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="11" t="inlineStr">
         <is>
-          <t>Determinism check: 10 eval invocations of nearmiss-film-rate on qwen3.5:9b (20 runs) gave 19 bit-identical and 1 divergent only in the final free-text iteration; load_duration flat 238-324ms throughout, so not a model reload.</t>
+          <t>v3 changes: fabricated arguments split into invented row id vs invented search term, and an answer truncated by the token cap can no longer be graded as a refusal. Regrading all 968 runs produced 0 correct/declined flips — both changes are additive.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="H42" s="11" t="inlineStr">
         <is>
-          <t>gpt-5.6-sol and gpt-5.6-terra were run later, on the same config (standard+desc, seed 42, temp 0, repeats 2, thinking off, 2500 max tokens, v1+v2) and graded live at v3. One config difference from the earlier GPT rows: the OpenAI client now retries 429/5xx with backoff, which affects resilience, not output.</t>
+          <t>Caveat on the hop columns: the v2 near-miss and truncation questions all sit at hop 2, so 'hop 2 ans' measures search recovery as much as depth. Chain-only scores are in RESULTS-ANALYSIS.md.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" s="11" t="inlineStr">
+        <is>
+          <t>Determinism check: 10 eval invocations of nearmiss-film-rate on qwen3.5:9b (20 runs) gave 19 bit-identical and 1 divergent only in the final free-text iteration; load_duration flat 238-324ms throughout, so not a model reload.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="H44" s="11" t="inlineStr">
+        <is>
+          <t>gpt-5.6-sol and gpt-5.6-terra were run later on the same config and graded live at v3. One config difference from the earlier GPT rows: the OpenAI client now retries 429/5xx with backoff, which affects resilience, not output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" s="11" t="inlineStr">
+        <is>
+          <t>phi4-mini (row 21) and the deepseek-r1 retest used Repeats=1 and MaxOutputTokens 6000. Their run COUNTS are therefore out of 21, not 42; rates are comparable, totals are not.</t>
         </is>
       </c>
     </row>

--- a/LlmMoveiAgentResults.xlsx
+++ b/LlmMoveiAgentResults.xlsx
@@ -7,30 +7,22 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="sql-shortcut control" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <b val="1"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -45,7 +37,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -64,6 +56,12 @@
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -77,36 +75,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -529,3488 +521,3644 @@
   <dimension ref="A1:AJ45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" style="7" min="1" max="1"/>
-    <col width="12" customWidth="1" style="7" min="2" max="2"/>
-    <col width="14.9" customWidth="1" style="7" min="3" max="3"/>
-    <col width="9.4" customWidth="1" style="7" min="4" max="4"/>
-    <col width="8.699999999999999" customWidth="1" style="7" min="5" max="5"/>
-    <col width="12.1" customWidth="1" style="7" min="6" max="6"/>
-    <col width="21" customWidth="1" style="7" min="7" max="7"/>
-    <col width="10.7" customWidth="1" style="7" min="8" max="8"/>
-    <col width="27.4" customWidth="1" style="7" min="9" max="9"/>
-    <col width="5.7" customWidth="1" style="7" min="10" max="10"/>
-    <col width="8.1" customWidth="1" style="7" min="11" max="11"/>
-    <col width="8.1" customWidth="1" style="7" min="12" max="12"/>
-    <col width="8.300000000000001" customWidth="1" style="7" min="13" max="13"/>
-    <col width="7" customWidth="1" style="7" min="14" max="14"/>
-    <col width="8.5" customWidth="1" style="7" min="15" max="15"/>
-    <col width="9" customWidth="1" style="7" min="16" max="16"/>
-    <col width="9" customWidth="1" style="7" min="17" max="17"/>
-    <col width="9" customWidth="1" style="7" min="18" max="18"/>
-    <col width="9" customWidth="1" style="7" min="19" max="19"/>
-    <col width="9.5" customWidth="1" style="7" min="20" max="20"/>
-    <col width="8" customWidth="1" style="7" min="21" max="21"/>
-    <col width="9" customWidth="1" style="7" min="22" max="22"/>
-    <col width="12" customWidth="1" style="7" min="23" max="23"/>
-    <col width="8.5" customWidth="1" style="7" min="24" max="24"/>
-    <col width="10" customWidth="1" style="7" min="25" max="25"/>
-    <col width="7.5" customWidth="1" style="7" min="26" max="26"/>
-    <col width="8.5" customWidth="1" style="7" min="27" max="27"/>
-    <col width="78" customWidth="1" style="7" min="36" max="36"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14.85546875" customWidth="1" min="3" max="3"/>
+    <col width="9.42578125" customWidth="1" min="4" max="4"/>
+    <col width="8.7109375" customWidth="1" min="5" max="5"/>
+    <col width="18.5703125" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="10.7109375" customWidth="1" min="8" max="8"/>
+    <col width="27.42578125" customWidth="1" min="9" max="9"/>
+    <col width="5.7109375" customWidth="1" min="10" max="10"/>
+    <col width="8.140625" customWidth="1" min="11" max="12"/>
+    <col width="8.28515625" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="8.42578125" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="19"/>
+    <col width="9.42578125" customWidth="1" min="20" max="20"/>
+    <col width="8" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="8.42578125" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="25" max="25"/>
+    <col width="7.42578125" customWidth="1" min="26" max="26"/>
+    <col width="8.42578125" customWidth="1" min="27" max="27"/>
+    <col width="78" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="12" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" s="12" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Variant </t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Parameters (b)</t>
         </is>
       </c>
-      <c r="D1" s="12" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Quant</t>
         </is>
       </c>
-      <c r="E1" s="12" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Size (gb)</t>
         </is>
       </c>
-      <c r="F1" s="12" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="G1" s="12" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Tag Name</t>
         </is>
       </c>
-      <c r="H1" s="12" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>GPU/CPU</t>
         </is>
       </c>
-      <c r="I1" s="12" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Output file</t>
         </is>
       </c>
-      <c r="J1" s="12" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Runs</t>
         </is>
       </c>
-      <c r="K1" s="12" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="L1" s="13" t="inlineStr">
+      <c r="L1" s="5" t="inlineStr">
         <is>
           <t>Strict</t>
         </is>
       </c>
-      <c r="M1" s="12" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Cap Hits</t>
         </is>
       </c>
-      <c r="N1" s="12" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Errors</t>
         </is>
       </c>
-      <c r="O1" s="12" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Emp. Ans</t>
         </is>
       </c>
-      <c r="P1" s="12" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Avg TC p/r</t>
         </is>
       </c>
-      <c r="Q1" s="12" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Avg TC p/i</t>
         </is>
       </c>
-      <c r="R1" s="12" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Repeated</t>
         </is>
       </c>
-      <c r="S1" s="12" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Tokens In</t>
         </is>
       </c>
-      <c r="T1" s="12" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Tokens Out</t>
         </is>
       </c>
-      <c r="U1" s="12" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>Fab. ID</t>
         </is>
       </c>
-      <c r="V1" s="12" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>Fab. Term</t>
         </is>
       </c>
-      <c r="W1" s="12" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>call id as arg</t>
         </is>
       </c>
-      <c r="X1" s="12" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>type m/m</t>
         </is>
       </c>
-      <c r="Y1" s="12" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>schema err.</t>
         </is>
       </c>
-      <c r="Z1" s="12" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>ref  /8</t>
         </is>
       </c>
-      <c r="AA1" s="12" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>over-ref</t>
         </is>
       </c>
-      <c r="AB1" s="12" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>hop 2 ans</t>
         </is>
       </c>
-      <c r="AC1" s="12" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>hop 2 nav</t>
         </is>
       </c>
-      <c r="AD1" s="12" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>hop 3 ans</t>
         </is>
       </c>
-      <c r="AE1" s="12" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>hop 3 nav</t>
         </is>
       </c>
-      <c r="AF1" s="12" t="inlineStr">
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>hop 4 ans</t>
         </is>
       </c>
-      <c r="AG1" s="12" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>hop 4 nav</t>
         </is>
       </c>
-      <c r="AH1" s="12" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>hop 5 ans</t>
         </is>
       </c>
-      <c r="AI1" s="12" t="inlineStr">
+      <c r="AI1" s="4" t="inlineStr">
         <is>
           <t>hop 5 nav</t>
         </is>
       </c>
-      <c r="AJ1" s="12" t="inlineStr">
+      <c r="AJ1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>Qwen2.5</t>
         </is>
       </c>
-      <c r="B2" s="11" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>1.5b</t>
         </is>
       </c>
-      <c r="C2" s="11" t="n">
+      <c r="C2" s="3" t="n">
         <v>1.54</v>
       </c>
-      <c r="D2" s="11" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E2" s="11" t="n">
+      <c r="E2" s="3" t="n">
         <v>0.98</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="6" t="n">
         <v>45536</v>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>qwen2.5:1.5b</t>
         </is>
       </c>
-      <c r="H2" s="11" t="n">
+      <c r="H2" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="11" t="inlineStr">
-        <is>
-          <t>Hard Fail - Didn't call tools</t>
-        </is>
-      </c>
-      <c r="AJ2" s="8" t="inlineStr">
-        <is>
-          <t>No run file on disk, so the hard fail cannot be verified from logs. Nothing to validate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="11" t="inlineStr">
+      <c r="I2" s="12" t="inlineStr">
+        <is>
+          <t>runs-20260814-122314.jsonl</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>3263</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>185</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="1" t="inlineStr">
+        <is>
+          <t>RUN AFTER THE FACT — the 'didn't call tools' label was WRONG and only running it showed that. It made 15 tool calls across 42 runs, 11 of which succeeded; 28 of 42 runs made none. Strict 0/42: both of its two 'correct' are nearmiss-film-language answered with ZERO tool calls, guessing 'English' from priors and appending the non-sequitur 'ERROR: The query returned no results.' — the expected answer happens to be English, so substring matching passed it. 10 of 42 runs print the tool DECLARATION schema back as text ('{"type": "function", "function": {search...'), i.e. it echoes the shape it was offered rather than issuing a call. 6 empty answers, 9 fabricated arguments (5 invented ids), 3 schema errors, 0/8 declines. Genuinely answered 0 of 34.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="90" customHeight="1">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="3" t="n">
         <v>3.09</v>
       </c>
-      <c r="D3" s="11" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n">
+      <c r="E3" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="6" t="n">
         <v>45536</v>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>qwen2.5:3b</t>
         </is>
       </c>
-      <c r="H3" s="11" t="n">
+      <c r="H3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I3" s="11" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-192641.jsonl</t>
         </is>
       </c>
-      <c r="J3" s="11" t="n">
+      <c r="J3" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="K3" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M3" s="11" t="n">
+      <c r="M3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="N3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="P3" s="11" t="n">
+      <c r="N3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" s="3" t="n">
         <v>3.79</v>
       </c>
-      <c r="Q3" s="11" t="n">
+      <c r="Q3" s="3" t="n">
         <v>1.64</v>
       </c>
-      <c r="R3" s="11" t="n">
+      <c r="R3" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="S3" s="11" t="n">
+      <c r="S3" s="3" t="n">
         <v>8666</v>
       </c>
-      <c r="T3" s="11" t="n">
+      <c r="T3" s="3" t="n">
         <v>268</v>
       </c>
-      <c r="U3" s="11" t="n">
+      <c r="U3" s="3" t="n">
         <v>67</v>
       </c>
-      <c r="V3" s="11" t="n">
+      <c r="V3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="W3" s="11" t="n">
+      <c r="W3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="X3" s="11" t="n">
+      <c r="X3" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="Y3" s="11" t="n">
+      <c r="Y3" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="Z3" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA3" s="11" t="n">
+      <c r="Z3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AB3" s="11" t="n">
+      <c r="AB3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC3" s="11" t="n">
+      <c r="AC3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AD3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ3" s="8" t="inlineStr">
+      <c r="AD3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 10/42 — 2 passes never reached the required tools (guessed get_film(123) on nearmiss-film-rate without searching). Worst argument discipline in the set, and it is the bad kind: 67 of its 78 fabricated arguments are invented row ids, not search terms. 51 schema errors, 53% of all tool calls errored, 34 blocked repeats. Sends literal placeholders as ids ('result of previous search_film call', '{{result.store_id}}'). Nothing above hop 2.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="11" t="inlineStr">
+    <row r="4" ht="60" customHeight="1">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>7b</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="3" t="n">
         <v>7.62</v>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E4" s="11" t="n">
+      <c r="E4" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="F4" s="14" t="n">
+      <c r="F4" s="6" t="n">
         <v>45536</v>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>qwen2.5:7b</t>
         </is>
       </c>
-      <c r="H4" s="11" t="n">
+      <c r="H4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-194621.jsonl</t>
         </is>
       </c>
-      <c r="J4" s="11" t="n">
+      <c r="J4" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K4" s="11" t="n">
+      <c r="K4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="11" t="n">
+      <c r="N4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>3.14</v>
       </c>
-      <c r="Q4" s="11" t="n">
+      <c r="Q4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R4" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="S4" s="11" t="n">
+      <c r="R4" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S4" s="3" t="n">
         <v>10684</v>
       </c>
-      <c r="T4" s="11" t="n">
+      <c r="T4" s="3" t="n">
         <v>143</v>
       </c>
-      <c r="U4" s="11" t="n">
+      <c r="U4" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="V4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="11" t="n">
+      <c r="V4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z4" s="15" t="n">
+      <c r="Z4" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="AA4" s="11" t="n">
+      <c r="AA4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AB4" s="11" t="n">
+      <c r="AB4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AC4" s="11" t="n">
+      <c r="AC4" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AD4" s="11" t="n">
+      <c r="AD4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AE4" s="11" t="n">
+      <c r="AE4" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AF4" s="11" t="n">
+      <c r="AF4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AG4" s="11" t="n">
+      <c r="AG4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AH4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ4" s="8" t="inlineStr">
+      <c r="AH4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" s="1" t="inlineStr">
         <is>
           <t>CORRECTION applied: 'ref /8' was 5, should be 8 — the JSONL records 8/8 correctly declined. Every other figure verified. Strict 24/42, no lucky passes. Solid mid-chain (hop3 6/10, hop4 5/6) but 0/4 at hop5 and 1/8 on near-miss recovery. All 18 fabricated arguments are invented ids. 2 cap hits.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Qwen3</t>
         </is>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>4b-instruct</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="3" t="n">
         <v>4.02</v>
       </c>
-      <c r="D5" s="11" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="3" t="n">
         <v>2.5</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="6" t="n">
         <v>45931</v>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>qwen3:4b-instruct</t>
         </is>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I5" s="11" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-195322.jsonl</t>
         </is>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="3" t="n">
         <v>29</v>
       </c>
-      <c r="M5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="11" t="n">
+      <c r="M5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="3" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R5" s="11" t="n">
+      <c r="R5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S5" s="11" t="n">
+      <c r="S5" s="3" t="n">
         <v>10766</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="T5" s="3" t="n">
         <v>266</v>
       </c>
-      <c r="U5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="11" t="n">
+      <c r="U5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA5" s="11" t="n">
+      <c r="AA5" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AB5" s="11" t="n">
+      <c r="AB5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC5" s="11" t="n">
+      <c r="AC5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AD5" s="11" t="n">
+      <c r="AD5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AE5" s="11" t="n">
+      <c r="AE5" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AF5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG5" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH5" s="11" t="n">
+      <c r="AF5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG5" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AI5" s="11" t="n">
+      <c r="AI5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AJ5" s="8" t="inlineStr">
+      <c r="AJ5" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 29/42, no lucky passes. Zero fabricated arguments of either kind, zero schema errors, 1 error in 103 calls — the cleanest small local model. Perfect refusal (8/8) but 10 over-refusals. 0/8 on near-miss recovery: gives up after one NO ROWS instead of shortening the search term.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>Qwen3.5</t>
         </is>
       </c>
-      <c r="B6" s="11" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>4b</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="3" t="n">
         <v>4.66</v>
       </c>
-      <c r="D6" s="11" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="6" t="n">
         <v>46143</v>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>qwen3.5:4b</t>
         </is>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="11" t="inlineStr">
+      <c r="I6" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-195952.jsonl</t>
         </is>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="N6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="11" t="n">
+      <c r="N6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="3" t="n">
         <v>4.95</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="3" t="n">
         <v>1.04</v>
       </c>
-      <c r="R6" s="11" t="n">
+      <c r="R6" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="S6" s="11" t="n">
+      <c r="S6" s="3" t="n">
         <v>18583</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="T6" s="3" t="n">
         <v>237</v>
       </c>
-      <c r="U6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="11" t="n">
+      <c r="U6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="11" t="n">
+      <c r="W6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AA6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB6" s="11" t="n">
+      <c r="AA6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AC6" s="11" t="n">
+      <c r="AC6" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AD6" s="11" t="n">
+      <c r="AD6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE6" s="11" t="n">
+      <c r="AE6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AF6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI6" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ6" s="8" t="inlineStr">
+      <c r="AF6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ6" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 32/42. Perfect 20/20 on pure dependency chains — equal to GPT-4o and gpt-5.4 on that axis, at 4B. 6/8 on near-miss recovery, beating every GPT-4o-class model. Fabrication is fully exonerated by the split: all 18 are invented SEARCH TERMS and zero are invented ids — that is hunting for entities that do not exist, not hallucinating rows. Never over-refuses (0) but rarely declines (2/8); burns iterations instead (8 cap hits, 28 blocked repeats). Bit-identical across repeats (a 20-run follow-up on qwen3.5:9b measured the qwen3.5 divergence rate at 1 in 20, confined to final-answer prose and flagged by a 12x latency outlier; tool calls never varied).</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="11" t="inlineStr">
+    <row r="7" ht="105" customHeight="1">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>9b</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="3" t="n">
         <v>9.65</v>
       </c>
-      <c r="D7" s="11" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="3" t="n">
         <v>6.6</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="6" t="n">
         <v>46143</v>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>qwen3.5:9b</t>
         </is>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I7" s="11" t="inlineStr">
+      <c r="I7" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-200504.jsonl</t>
         </is>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="3" t="n">
         <v>38</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="N7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" s="11" t="n">
+      <c r="N7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
         <v>4.81</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="3" t="n">
         <v>1.15</v>
       </c>
-      <c r="R7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="11" t="n">
+      <c r="R7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="3" t="n">
         <v>17160</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="T7" s="3" t="n">
         <v>320</v>
       </c>
-      <c r="U7" s="11" t="n">
+      <c r="U7" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="V7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="W7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="11" t="n">
+      <c r="W7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AC7" s="11" t="n">
+      <c r="AC7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AD7" s="11" t="n">
+      <c r="AD7" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE7" s="11" t="n">
+      <c r="AE7" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AF7" s="11" t="n">
+      <c r="AF7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AG7" s="11" t="n">
+      <c r="AG7" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AH7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI7" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ7" s="8" t="inlineStr">
+      <c r="AH7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ7" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 38/42 — best non-GPT, and beats GPT-4o (31), GPT-4o-mini (28) and gpt-5.5 (36). Perfect on every answerable question: 34/34, incl. 20/20 chains, 8/8 near-miss, 4/4 fan-out, 4/4 hop5. All 4 losses are refusal cases it tried to answer; never over-refuses. Its 48 fabricated arguments split 34 id / 14 term, but 32 of the 34 ids are a sequential sweep of get_category(category_id=1..16) on decline-easy-category, using bounds the tool itself advertises — exhaustive enumeration, not hallucination. Only 2 loose invented ids in 42 runs. Slowest local model at 10.2s/run.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="11" t="inlineStr">
+    <row r="8" ht="60" customHeight="1">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>2b</t>
         </is>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="D8" s="11" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>Q8_0</t>
         </is>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="3" t="n">
         <v>2.7</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="6" t="n">
         <v>46143</v>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>qwen3.5:2b</t>
         </is>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I8" s="11" t="inlineStr">
+      <c r="I8" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-201510.jsonl</t>
         </is>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="11" t="n">
+      <c r="M8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="3" t="n">
         <v>5.48</v>
       </c>
-      <c r="Q8" s="11" t="n">
+      <c r="Q8" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="R8" s="11" t="n">
+      <c r="R8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="S8" s="11" t="n">
+      <c r="S8" s="3" t="n">
         <v>19405</v>
       </c>
-      <c r="T8" s="11" t="n">
+      <c r="T8" s="3" t="n">
         <v>375</v>
       </c>
-      <c r="U8" s="11" t="n">
+      <c r="U8" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="V8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="W8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="11" t="n">
+      <c r="W8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB8" s="11" t="n">
+      <c r="Z8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AC8" s="11" t="n">
+      <c r="AC8" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AD8" s="11" t="n">
+      <c r="AD8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AE8" s="11" t="n">
+      <c r="AE8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AF8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG8" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" s="11" t="n">
+      <c r="AF8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ8" s="8" t="inlineStr">
+      <c r="AJ8" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 20/42. Chain 14/20 but 0/8 near-miss and 0/4 fan-out. 24 fabricated arguments lean toward search terms (16 term / 8 id). 4 cap hits, 16 blocked repeats — loops on failed searches with case variants ('SteepPUNK', 'Steeppunk'). Deterministic across repeats.</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="11" t="inlineStr">
+    <row r="9" ht="75" customHeight="1">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>2b-q4_K_M</t>
         </is>
       </c>
-      <c r="C9" s="11" t="n">
+      <c r="C9" s="3" t="n">
         <v>2.27</v>
       </c>
-      <c r="D9" s="11" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="3" t="n">
         <v>1.9</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="6" t="n">
         <v>46143</v>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>qwen3.5:2b-q4_K_M</t>
         </is>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I9" s="11" t="inlineStr">
+      <c r="I9" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-202235.jsonl</t>
         </is>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" s="11" t="n">
+      <c r="N9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="3" t="n">
         <v>7.43</v>
       </c>
-      <c r="Q9" s="11" t="n">
+      <c r="Q9" s="3" t="n">
         <v>1.21</v>
       </c>
-      <c r="R9" s="11" t="n">
+      <c r="R9" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="S9" s="11" t="n">
+      <c r="S9" s="3" t="n">
         <v>24309</v>
       </c>
-      <c r="T9" s="11" t="n">
+      <c r="T9" s="3" t="n">
         <v>431</v>
       </c>
-      <c r="U9" s="11" t="n">
+      <c r="U9" s="3" t="n">
         <v>66</v>
       </c>
-      <c r="V9" s="11" t="n">
+      <c r="V9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="11" t="n">
+      <c r="W9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AC9" s="11" t="n">
+      <c r="AC9" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AD9" s="11" t="n">
+      <c r="AD9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE9" s="11" t="n">
+      <c r="AE9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AF9" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG9" s="11" t="n">
+      <c r="AF9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AH9" s="11" t="n">
+      <c r="AH9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AI9" s="11" t="n">
+      <c r="AI9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ9" s="8" t="inlineStr">
+      <c r="AJ9" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 20/42 (2 lucky). Q4 against the Q8 build of the same 2B: raw score +2, but cap hits 4x worse (16 vs 4) and fabricated arguments 3.7x (88 vs 24) — and the split shows the damage is id-side, 66 invented ids against the Q8 build's 8. Called get_film 114 times brute-forcing ids. Never declines (0/8), never over-refuses (0). Quantisation cost shows up as loop control, not knowledge.</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+    <row r="10" ht="105" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>LLama3.1</t>
         </is>
       </c>
-      <c r="B10" s="11" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="C10" s="11" t="n">
+      <c r="C10" s="3" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="6" t="n">
         <v>45597</v>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>llama3.1</t>
         </is>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="I10" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-210354.jsonl</t>
         </is>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="K10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="L10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" s="11" t="n">
+      <c r="L10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
         <v>3.98</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="3" t="n">
         <v>3.98</v>
       </c>
-      <c r="R10" s="11" t="n">
+      <c r="R10" s="3" t="n">
         <v>65</v>
       </c>
-      <c r="S10" s="11" t="n">
+      <c r="S10" s="3" t="n">
         <v>3117</v>
       </c>
-      <c r="T10" s="11" t="n">
+      <c r="T10" s="3" t="n">
         <v>352</v>
       </c>
-      <c r="U10" s="11" t="n">
+      <c r="U10" s="3" t="n">
         <v>138</v>
       </c>
-      <c r="V10" s="11" t="n">
+      <c r="V10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="W10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" s="11" t="n">
+      <c r="W10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="Y10" s="11" t="n">
+      <c r="Y10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Z10" s="11" t="n">
+      <c r="Z10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" s="11" t="n">
+      <c r="AA10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="AB10" s="11" t="n">
+      <c r="AB10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AC10" s="11" t="n">
+      <c r="AC10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE10" s="11" t="n">
+      <c r="AD10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AF10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" s="8" t="inlineStr">
+      <c r="AF10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="1" t="inlineStr">
         <is>
           <t>Verified, but the raw 9 is misleading — strict 4/42, the biggest inflation in the set. 5 of the 9 passes never reached the required tools: it calls get_film(film_id=1), and film 1 happens to be English with rental_duration 6, which are the expected answers to two near-miss questions. Genuinely answered 1 of 34. The worst fabricator in the sweep and unambiguously so: 138 of 145 are invented row ids with no enumeration pattern behind them. 96 errored calls (58%), 65 blocked repeats. Fires ~4 calls in one iteration then stops — no read-then-plan loop. 16 over-refusals.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>LLama3.2</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>3b</t>
         </is>
       </c>
-      <c r="C11" s="11" t="n">
+      <c r="C11" s="3" t="n">
         <v>3.21</v>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="6" t="n">
         <v>45536</v>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>llama3.2</t>
         </is>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I11" s="11" t="inlineStr">
+      <c r="I11" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-211038.jsonl</t>
         </is>
       </c>
-      <c r="J11" s="11" t="n">
+      <c r="J11" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" s="11" t="n">
+      <c r="K11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="Q11" s="11" t="n">
+      <c r="Q11" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="11" t="n">
+      <c r="R11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3" t="n">
         <v>2828</v>
       </c>
-      <c r="T11" s="11" t="n">
+      <c r="T11" s="3" t="n">
         <v>77</v>
       </c>
-      <c r="U11" s="11" t="n">
+      <c r="U11" s="3" t="n">
         <v>20</v>
       </c>
-      <c r="V11" s="11" t="n">
+      <c r="V11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="W11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" s="11" t="n">
+      <c r="W11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Y11" s="11" t="n">
+      <c r="Y11" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="Z11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA11" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ11" s="8" t="inlineStr">
+      <c r="Z11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 4/42, all 4 refusals — answered 0 of 34. Exactly one tool call per run, then stops. 57% of calls errored: passes titles where ids are required ('AGENT TRUMAN' as film_id) and wrong parameter names (title_contains to get_film). Never chains.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="12" ht="60" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Mistral-Nemo</t>
         </is>
       </c>
-      <c r="B12" s="11" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>12b</t>
         </is>
       </c>
-      <c r="C12" s="11" t="n">
+      <c r="C12" s="3" t="n">
         <v>12.2</v>
       </c>
-      <c r="D12" s="11" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Q4_0</t>
         </is>
       </c>
-      <c r="E12" s="11" t="n">
+      <c r="E12" s="3" t="n">
         <v>7.1</v>
       </c>
-      <c r="F12" s="14" t="n">
+      <c r="F12" s="6" t="n">
         <v>45839</v>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>mistral-nemo:12b</t>
         </is>
       </c>
-      <c r="H12" s="11" t="n">
+      <c r="H12" s="3" t="n">
         <v>0.73</v>
       </c>
-      <c r="I12" s="11" t="inlineStr">
+      <c r="I12" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-211409.jsonl</t>
         </is>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K12" s="11" t="n">
+      <c r="K12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="L12" s="11" t="n">
+      <c r="L12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="M12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="11" t="n">
+      <c r="M12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="3" t="n">
         <v>1.05</v>
       </c>
-      <c r="R12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="11" t="n">
+      <c r="R12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="n">
         <v>2501</v>
       </c>
-      <c r="T12" s="11" t="n">
+      <c r="T12" s="3" t="n">
         <v>58</v>
       </c>
-      <c r="U12" s="11" t="n">
+      <c r="U12" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="V12" s="11" t="n">
+      <c r="V12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="11" t="n">
+      <c r="W12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z12" s="11" t="n">
+      <c r="Z12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA12" s="11" t="n">
+      <c r="AA12" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AB12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="11" t="n">
+      <c r="AB12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AF12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="8" t="inlineStr">
+      <c r="AF12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 6/42, all 6 refusals — answered 0 of 34, despite being the largest local model tested. 1.05 calls/run, 2.0 iterations/run: one call, then it answers. Only 2 errored calls, so it is not malformed — it simply never takes a second hop. 12 over-refusals.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>Mistral</t>
         </is>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="C13" s="11" t="n">
+      <c r="C13" s="3" t="n">
         <v>7.25</v>
       </c>
-      <c r="D13" s="11" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="3" t="n">
         <v>4.4</v>
       </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="6" t="n">
         <v>45839</v>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>mistral</t>
         </is>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="11" t="inlineStr">
-        <is>
-          <t>Hard Fail - Didn't call tools</t>
-        </is>
-      </c>
-      <c r="AJ13" s="8" t="inlineStr">
-        <is>
-          <t>No run file on disk, so the hard fail cannot be verified from logs. Nothing to validate.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="I13" s="12" t="inlineStr">
+        <is>
+          <t>runs-20260814-122421.jsonl</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>2743</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="1" t="inlineStr">
+        <is>
+          <t>RUN AFTER THE FACT — label CONFIRMED. Zero tool calls in all 42 runs, wire-checked: 25 tool definitions sent in correct Ollama format, no tool_calls field in the response. Belongs with granite3.3:8b, command-r7b, deepseek-r1:8b and phi4-mini. Its failure mode is its own though: 31 of 42 runs write pseudo-code function calls inside markdown fences — ```search_film(title_contains="alamo videotape")``` — then continue as if they had run, prefaced with 'Assuming...'. Both of its 2 correct are genuine refusals on unreachable-total-film-count ('there's no tool that directly...'), so strict 2/42 but genuinely answered 0 of 34. Declares the 'tools' capability and its template handles them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="75" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>Ministral</t>
         </is>
       </c>
-      <c r="B14" s="11" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>latest</t>
         </is>
       </c>
-      <c r="C14" s="11" t="n">
+      <c r="C14" s="3" t="n">
         <v>8.92</v>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E14" s="11" t="n">
+      <c r="E14" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="6" t="n">
         <v>45992</v>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>ministral-3</t>
         </is>
       </c>
-      <c r="H14" s="11" t="n">
+      <c r="H14" s="3" t="n">
         <v>0.92</v>
       </c>
-      <c r="I14" s="11" t="inlineStr">
+      <c r="I14" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-212008.jsonl</t>
         </is>
       </c>
-      <c r="J14" s="11" t="n">
+      <c r="J14" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K14" s="11" t="n">
+      <c r="K14" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="L14" s="11" t="n">
+      <c r="L14" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="M14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" s="11" t="n">
+      <c r="M14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3" t="n">
         <v>2.43</v>
       </c>
-      <c r="Q14" s="11" t="n">
+      <c r="Q14" s="3" t="n">
         <v>1.11</v>
       </c>
-      <c r="R14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="11" t="n">
+      <c r="R14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="n">
         <v>8146</v>
       </c>
-      <c r="T14" s="11" t="n">
+      <c r="T14" s="3" t="n">
         <v>110</v>
       </c>
-      <c r="U14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="11" t="n">
+      <c r="U14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA14" s="11" t="n">
+      <c r="AA14" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AB14" s="11" t="n">
+      <c r="AB14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC14" s="11" t="n">
+      <c r="AC14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AD14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AF14" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG14" s="11" t="n">
+      <c r="AD14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AH14" s="11" t="n">
+      <c r="AH14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AI14" s="11" t="n">
+      <c r="AI14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ14" s="8" t="inlineStr">
+      <c r="AJ14" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 24/42 (2 lucky on hop4-customer-country). Zero fabricated arguments of either kind, zero schema errors, zero tool errors across 102 calls — the cleanest caller in the set. Perfect refusal 8/8 but 10 over-refusals. A second full run (runs-20260812-214734.jsonl) scored an identical 26/42 with the same per-hop split, so this result is reproducible.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+    <row r="15" ht="90" customHeight="1">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>Granite3.3</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="C15" s="11" t="n">
+      <c r="C15" s="3" t="n">
         <v>8.17</v>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="3" t="n">
         <v>4.9</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="6" t="n">
         <v>45748</v>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>granite3.3:8b</t>
         </is>
       </c>
-      <c r="H15" s="11" t="n">
+      <c r="H15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I15" s="11" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-213730.jsonl</t>
         </is>
       </c>
-      <c r="J15" s="11" t="n">
+      <c r="J15" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K15" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L15" s="11" t="n">
+      <c r="K15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="M15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="11" t="n">
+      <c r="M15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3" t="n">
         <v>2559</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="T15" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="U15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="11" t="n">
+      <c r="U15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AA15" s="11" t="n">
+      <c r="AA15" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="AB15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="11" t="n">
+      <c r="AB15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AE15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="8" t="inlineStr">
+      <c r="AE15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls in all 42 runs, wire-confirmed. Strict 3/42 and answered 0 of 34. It prints tool calls as prose ('&lt;|tool call{...}|&gt;' and json blocks) in 17 runs instead of using the tool-call channel. Re-ran with wire capture: 25 tool definitions were sent correctly and it described them accurately, then called none — model behaviour, not a harness fault. Its 4 'correct' include 2 grader false positives. The numbers here are real but should be read as a hard fail, not a low score.</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+    <row r="16" ht="75" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>Command R</t>
         </is>
       </c>
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>7b</t>
         </is>
       </c>
-      <c r="C16" s="11" t="n">
+      <c r="C16" s="3" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E16" s="11" t="n">
+      <c r="E16" s="3" t="n">
         <v>5.1</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="6" t="n">
         <v>45658</v>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
         <is>
           <t>command-r7b</t>
         </is>
       </c>
-      <c r="H16" s="11" t="n">
+      <c r="H16" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I16" s="11" t="inlineStr">
+      <c r="I16" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-214520.jsonl</t>
         </is>
       </c>
-      <c r="J16" s="11" t="n">
+      <c r="J16" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K16" s="11" t="n">
+      <c r="K16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="M16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="11" t="n">
+      <c r="M16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="3" t="n">
         <v>3452</v>
       </c>
-      <c r="T16" s="11" t="n">
+      <c r="T16" s="3" t="n">
         <v>40</v>
       </c>
-      <c r="U16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="11" t="n">
+      <c r="U16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA16" s="11" t="n">
+      <c r="AA16" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="AB16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ16" s="8" t="inlineStr">
+      <c r="AB16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls in all 42 runs, wire-confirmed (25 tools sent, none called). Strict 8/42, but all 8 are refusals; it answered 0 of 34 and refused 33 of 34 answerable questions ('I don't have access to information about...'). Its perfect 8/8 refusal score is the clearest demonstration here that refusal accuracy is meaningless without the over-refusal denominator.</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="75" customHeight="1">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>Gemma4</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>e2b</t>
         </is>
       </c>
-      <c r="C17" s="11" t="n">
+      <c r="C17" s="3" t="n">
         <v>5.12</v>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E17" s="11" t="n">
+      <c r="E17" s="3" t="n">
         <v>7.2</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="6" t="n">
         <v>46174</v>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
         <is>
           <t>gemma4:e2b</t>
         </is>
       </c>
-      <c r="H17" s="11" t="n">
+      <c r="H17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I17" s="11" t="inlineStr">
+      <c r="I17" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-215050.jsonl</t>
         </is>
       </c>
-      <c r="J17" s="11" t="n">
+      <c r="J17" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K17" s="11" t="n">
+      <c r="K17" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L17" s="11" t="n">
+      <c r="L17" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="M17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="11" t="n">
+      <c r="M17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P17" s="11" t="n">
+      <c r="P17" s="3" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q17" s="11" t="n">
+      <c r="Q17" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" s="11" t="n">
+      <c r="R17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="3" t="n">
         <v>8107</v>
       </c>
-      <c r="T17" s="11" t="n">
+      <c r="T17" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="U17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="11" t="n">
+      <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA17" s="11" t="n">
+      <c r="AA17" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AB17" s="11" t="n">
+      <c r="AB17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC17" s="11" t="n">
+      <c r="AC17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AD17" s="11" t="n">
+      <c r="AD17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AE17" s="11" t="n">
+      <c r="AE17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AF17" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG17" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ17" s="8" t="inlineStr">
+      <c r="AF17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG17" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 28/42, no lucky passes. Zero fabricated arguments, zero schema errors, zero tool errors. Beats its larger sibling e4b (26). Chain 18/20 but 0/8 near-miss and 0/4 fan-out — it fails only where recovery or breadth is needed. 12 over-refusals is the price of its 8/8 refusal. The 2 empty answers are clean stops after one call, not truncation.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="11" t="inlineStr">
+    <row r="18" ht="60" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>e4b</t>
         </is>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E18" s="11" t="n">
+      <c r="E18" s="3" t="n">
         <v>9.6</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="6" t="n">
         <v>46174</v>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>gemma4:e4b</t>
         </is>
       </c>
-      <c r="H18" s="11" t="n">
+      <c r="H18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I18" s="11" t="inlineStr">
+      <c r="I18" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-221036.jsonl</t>
         </is>
       </c>
-      <c r="J18" s="11" t="n">
+      <c r="J18" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K18" s="11" t="n">
+      <c r="K18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="3" t="n">
         <v>26</v>
       </c>
-      <c r="M18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="11" t="n">
+      <c r="M18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="P18" s="11" t="n">
+      <c r="P18" s="3" t="n">
         <v>2.43</v>
       </c>
-      <c r="Q18" s="11" t="n">
+      <c r="Q18" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" s="11" t="n">
+      <c r="R18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="n">
         <v>9442</v>
       </c>
-      <c r="T18" s="11" t="n">
+      <c r="T18" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="U18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z18" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA18" s="11" t="n">
+      <c r="U18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AB18" s="11" t="n">
+      <c r="AB18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC18" s="11" t="n">
+      <c r="AC18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AD18" s="11" t="n">
+      <c r="AD18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AE18" s="11" t="n">
+      <c r="AE18" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AF18" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG18" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH18" s="11" t="n">
+      <c r="AF18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AI18" s="11" t="n">
+      <c r="AI18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ18" s="8" t="inlineStr">
+      <c r="AJ18" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 26/42. Scores below the smaller e2b (28): more answers right (22 vs 20) but fewer refusals (4/8 vs 8/8). Same clean discipline — 0 fabricated, 0 schema errors, 0 tool errors. Both empty answers are on nearmiss-word-order and identical across repeats.</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="19" ht="90" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>Hermes3</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="C19" s="11" t="n">
+      <c r="C19" s="3" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="D19" s="11" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>Q4_0</t>
         </is>
       </c>
-      <c r="E19" s="11" t="n">
+      <c r="E19" s="3" t="n">
         <v>4.7</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="6" t="n">
         <v>45627</v>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="3" t="inlineStr">
         <is>
           <t>hermes3:8b</t>
         </is>
       </c>
-      <c r="H19" s="11" t="n">
+      <c r="H19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I19" s="11" t="inlineStr">
+      <c r="I19" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-215655.jsonl</t>
         </is>
       </c>
-      <c r="J19" s="11" t="n">
+      <c r="J19" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K19" s="11" t="n">
+      <c r="K19" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="L19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="M19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="11" t="n">
+      <c r="L19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="P19" s="11" t="n">
+      <c r="P19" s="3" t="n">
         <v>0.93</v>
       </c>
-      <c r="Q19" s="11" t="n">
+      <c r="Q19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="R19" s="11" t="n">
+      <c r="R19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="S19" s="11" t="n">
+      <c r="S19" s="3" t="n">
         <v>4254</v>
       </c>
-      <c r="T19" s="11" t="n">
+      <c r="T19" s="3" t="n">
         <v>111</v>
       </c>
-      <c r="U19" s="11" t="n">
+      <c r="U19" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="V19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" s="11" t="n">
+      <c r="V19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="X19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="11" t="n">
+      <c r="X19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z19" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA19" s="11" t="n">
+      <c r="Z19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AB19" s="11" t="n">
+      <c r="AB19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AC19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" s="11" t="n">
+      <c r="AC19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AE19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ19" s="8" t="inlineStr">
+      <c r="AE19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 4/42 (3 lucky) — answered 0 of 34. Leaks the harness's own tool-call envelope back as arguments, sending {'Arguments':{...},'CallId':'call_2','FunctionName':'get_staff'} as the argument object. That is why its 21 fabricated arguments split to only 11 id and 0 term: the other 10 are on parameter names no tool declares, which is also the whole of its schema-error count. 13 of 42 runs made no tool call at all.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+    <row r="20" ht="240" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>Deepseek R1</t>
         </is>
       </c>
-      <c r="B20" s="11" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>8b</t>
         </is>
       </c>
-      <c r="C20" s="11" t="n">
+      <c r="C20" s="3" t="n">
         <v>8.19</v>
       </c>
-      <c r="D20" s="11" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E20" s="11" t="n">
+      <c r="E20" s="3" t="n">
         <v>5.2</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="6" t="n">
         <v>45839</v>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
         <is>
           <t>deepseek-r1:8b</t>
         </is>
       </c>
-      <c r="H20" s="11" t="n">
+      <c r="H20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I20" s="11" t="inlineStr">
+      <c r="I20" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-221909.jsonl</t>
         </is>
       </c>
-      <c r="J20" s="11" t="n">
+      <c r="J20" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K20" s="11" t="n">
+      <c r="K20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L20" s="11" t="n">
+      <c r="L20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="11" t="n">
+      <c r="M20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="P20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="11" t="n">
+      <c r="P20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="n">
         <v>314</v>
       </c>
-      <c r="T20" s="11" t="n">
+      <c r="T20" s="3" t="n">
         <v>2298</v>
       </c>
-      <c r="U20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="11" t="n">
+      <c r="U20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AA20" s="11" t="n">
+      <c r="AA20" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI20" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ20" s="8" t="inlineStr">
+      <c r="AB20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls, wire-confirmed, at BOTH token caps. Strict 1/42 and its true score is 0: the single point is a grader artefact (a complete sentence containing the conditional 'I cannot proceed further without guessing', inside a plan it never executed, read as a refusal). RETEST: re-run at MaxOutputTokens 6000 (runs-20260813-162941.jsonl, 21 questions x 1 repeat) to test whether the 2500 cap was the cause. It was not. Truncation fell from 31/42 to 3/21 and empty answers from 31 to 3, so the cap was a real constraint — but tool calls stayed at ZERO and the score did not move. Every run is one iteration: no tool call means nothing to feed back. It writes an essay about calling tools instead (309,720 chars of reasoning vs 10,186 of answer) naming tools that mostly do not exist (search_film_by_title, get_rental_film_id). Wire at 6000: 25 tools sent, no tool_calls field, 11,497 chars of 'thinking', content ending '&lt;tool&gt;search_film_by_title&lt;/tool&gt;' — its own invented pseudo-syntax in the content channel. Also ignores Agent:Thinking=false entirely (reasoning in every iteration). Costs 50% more wall clock at the higher cap for an identical zero. The earlier 'untestable at this MaxOutputTokens' caveat is retired — the cap was hiding the failure, not causing it.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="21" ht="300" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Phi4</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>mini</t>
         </is>
       </c>
-      <c r="C21" s="11" t="n">
+      <c r="C21" s="3" t="n">
         <v>3.8</v>
       </c>
-      <c r="D21" s="11" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Q4_K_M</t>
         </is>
       </c>
-      <c r="E21" s="11" t="n">
+      <c r="E21" s="3" t="n">
         <v>2.32</v>
       </c>
-      <c r="F21" s="16" t="n">
+      <c r="F21" s="8" t="n">
         <v>45689</v>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>phi4-mini</t>
         </is>
       </c>
-      <c r="H21" s="11" t="n">
+      <c r="H21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="I21" s="11" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
         <is>
           <t>runs-20260813-165949.jsonl</t>
         </is>
       </c>
-      <c r="J21" s="11" t="n">
+      <c r="J21" s="3" t="n">
         <v>21</v>
       </c>
-      <c r="K21" s="11" t="n">
+      <c r="K21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="L21" s="11" t="n">
+      <c r="L21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="M21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="11" t="n">
+      <c r="M21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="3" t="n">
         <v>2289</v>
       </c>
-      <c r="T21" s="11" t="n">
+      <c r="T21" s="3" t="n">
         <v>113</v>
       </c>
-      <c r="U21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" s="11" t="n">
+      <c r="U21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AA21" s="11" t="n">
+      <c r="AA21" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AB21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" s="8" t="inlineStr">
+      <c r="AB21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls in all 21 runs, wire-confirmed. True score 0/21: the single 'correct' is the same planning-monologue false positive as deepseek-r1. NOTE THE DIFFERENT CONFIG: Repeats=1 (21 runs, not 42) and MaxOutputTokens 6000, so the counts here are not directly comparable with the rows above; the rates are. Distinct from the other zero-call failures and the closest call of the four: it emits STRUCTURALLY CORRECT tool-call JSON — [{"name": "get_film", "arguments": {"film_id": 1}}] — with real tool and parameter names, but into the content channel (15 of 21 runs). Checked properly because that shape suggests a rig fault: /api/show reports phi4-mini declares the 'tools' capability and its template does handle them, rendering tools into &lt;|tool|&gt;...&lt;|/tool|&gt; and expecting calls back wrapped as &lt;|tool_call|&gt;[...]&lt;|/tool_call|&gt;. Wire capture: 25 tools sent, no tool_calls field in the response, and the content carries the bare JSON array with NO &lt;|tool_call|&gt; delimiter. So the model omits the delimiter its own chat template requires and Ollama cannot parse the payload — a model failure, but one pair of tags away from working. Two aggravating factors: it also hallucinates the RESULTS, roleplaying whole conversations with invented rows (invents the city 'Springfield', invents actor ids [1,2,3] then concludes '3 actors'), and its text-format calls are frequently malformed anyway ({"arguments"} as a second object rather than a key; "parameters" instead of "arguments"). Invents tools that do not exist (search_rental, search_inventory_item). Fast and cheap at 113 output tokens and 2.0s per run, which buys nothing.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+    <row r="22" ht="75" customHeight="1">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>GPT</t>
         </is>
       </c>
-      <c r="B22" s="11" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>4o</t>
         </is>
       </c>
-      <c r="C22" s="11" t="inlineStr">
+      <c r="C22" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E22" s="11" t="inlineStr">
+      <c r="E22" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F22" s="11" t="inlineStr">
+      <c r="F22" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>gpt-4o</t>
         </is>
       </c>
-      <c r="H22" s="11" t="inlineStr">
+      <c r="H22" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I22" s="11" t="inlineStr">
+      <c r="I22" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-224947.jsonl</t>
         </is>
       </c>
-      <c r="J22" s="11" t="n">
+      <c r="J22" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K22" s="11" t="n">
+      <c r="K22" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="3" t="n">
         <v>31</v>
       </c>
-      <c r="M22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" s="11" t="n">
+      <c r="M22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
         <v>2.67</v>
       </c>
-      <c r="Q22" s="11" t="n">
+      <c r="Q22" s="3" t="n">
         <v>1.17</v>
       </c>
-      <c r="R22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" s="11" t="n">
+      <c r="R22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="n">
         <v>7003</v>
       </c>
-      <c r="T22" s="11" t="n">
+      <c r="T22" s="3" t="n">
         <v>73</v>
       </c>
-      <c r="U22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" s="11" t="n">
+      <c r="U22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AA22" s="11" t="n">
+      <c r="AA22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AB22" s="11" t="n">
+      <c r="AB22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC22" s="11" t="n">
+      <c r="AC22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AD22" s="11" t="n">
+      <c r="AD22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AE22" s="11" t="n">
+      <c r="AE22" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AF22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI22" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ22" s="8" t="inlineStr">
+      <c r="AF22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI22" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ22" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 31/42. Perfect 20/20 on dependency chains and 4/4 at hop 5, but 0/8 on near-miss recovery — the one axis where 4B local models clearly beat it (qwen3.5:4b 6/8, 9b 8/8). Zero fabricated arguments. The first attempt at this sweep (runs-20260812-224854.jsonl) errored 42/42 on rate limiting; this file is the clean re-run. Still the slowest GPT at 545s vs ~150s, consistent with retry backoff.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="11" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>4o-mini</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E23" s="11" t="inlineStr">
+      <c r="E23" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F23" s="11" t="inlineStr">
+      <c r="F23" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>gpt-4o-mini</t>
         </is>
       </c>
-      <c r="H23" s="11" t="inlineStr">
+      <c r="H23" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I23" s="11" t="inlineStr">
+      <c r="I23" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-230517.jsonl</t>
         </is>
       </c>
-      <c r="J23" s="11" t="n">
+      <c r="J23" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K23" s="11" t="n">
+      <c r="K23" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="3" t="n">
         <v>28</v>
       </c>
-      <c r="M23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" s="11" t="n">
+      <c r="M23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
         <v>3.26</v>
       </c>
-      <c r="Q23" s="11" t="n">
+      <c r="Q23" s="3" t="n">
         <v>1.33</v>
       </c>
-      <c r="R23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" s="11" t="n">
+      <c r="R23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3" t="n">
         <v>7414</v>
       </c>
-      <c r="T23" s="11" t="n">
+      <c r="T23" s="3" t="n">
         <v>88</v>
       </c>
-      <c r="U23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA23" s="11" t="n">
+      <c r="U23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA23" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AB23" s="11" t="n">
+      <c r="AB23" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC23" s="11" t="n">
+      <c r="AC23" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AD23" s="11" t="n">
+      <c r="AD23" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AE23" s="11" t="n">
+      <c r="AE23" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AF23" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG23" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH23" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI23" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ23" s="8" t="inlineStr">
+      <c r="AF23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ23" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 28/42. Same shape as gpt-4o on chains (20/20) and near-miss (0/8), losing ground only on refusal (4/8 vs 7/8). Fastest GPT run at 146s.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="11" t="inlineStr">
+    <row r="24" ht="45" customHeight="1">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>5.6 luna</t>
         </is>
       </c>
-      <c r="C24" s="11" t="inlineStr">
+      <c r="C24" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D24" s="11" t="inlineStr">
+      <c r="D24" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E24" s="11" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F24" s="11" t="inlineStr">
+      <c r="F24" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>gpt-5.6-luna</t>
         </is>
       </c>
-      <c r="H24" s="11" t="inlineStr">
+      <c r="H24" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I24" s="11" t="inlineStr">
+      <c r="I24" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-230934.jsonl</t>
         </is>
       </c>
-      <c r="J24" s="11" t="n">
+      <c r="J24" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K24" s="11" t="n">
+      <c r="K24" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="L24" s="11" t="n">
+      <c r="L24" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="M24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" s="11" t="n">
+      <c r="M24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
         <v>3.19</v>
       </c>
-      <c r="Q24" s="11" t="n">
+      <c r="Q24" s="3" t="n">
         <v>1.18</v>
       </c>
-      <c r="R24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="11" t="n">
+      <c r="R24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="n">
         <v>8330</v>
       </c>
-      <c r="T24" s="11" t="n">
+      <c r="T24" s="3" t="n">
         <v>89</v>
       </c>
-      <c r="U24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="11" t="n">
+      <c r="U24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA24" s="11" t="n">
+      <c r="AA24" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB24" s="11" t="n">
+      <c r="AB24" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="AC24" s="11" t="n">
+      <c r="AC24" s="3" t="n">
         <v>11</v>
       </c>
-      <c r="AD24" s="11" t="n">
+      <c r="AD24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE24" s="11" t="n">
+      <c r="AE24" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AF24" s="11" t="n">
+      <c r="AF24" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AG24" s="11" t="n">
+      <c r="AG24" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AH24" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI24" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ24" s="8" t="inlineStr">
+      <c r="AH24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI24" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ24" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 37/42. Chain 20/20, fan-out 4/4, near-miss 5/8. Loses 3 runs to over-refusal and both repeats of decline-easy-category. Second-best refusal calibration after gpt-5.4.</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="11" t="inlineStr">
+    <row r="25" ht="75" customHeight="1">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>5-4 std</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D25" s="11" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E25" s="11" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F25" s="11" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>gpt-5.4</t>
         </is>
       </c>
-      <c r="H25" s="11" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I25" s="11" t="inlineStr">
+      <c r="I25" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-231344.jsonl</t>
         </is>
       </c>
-      <c r="J25" s="11" t="n">
+      <c r="J25" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K25" s="11" t="n">
+      <c r="K25" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L25" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="M25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" s="11" t="n">
+      <c r="M25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q25" s="11" t="n">
+      <c r="Q25" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="R25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="11" t="n">
+      <c r="R25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3" t="n">
         <v>8562</v>
       </c>
-      <c r="T25" s="11" t="n">
+      <c r="T25" s="3" t="n">
         <v>98</v>
       </c>
-      <c r="U25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="11" t="n">
+      <c r="U25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" s="11" t="n">
+      <c r="AA25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AC25" s="11" t="n">
+      <c r="AC25" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AD25" s="11" t="n">
+      <c r="AD25" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE25" s="11" t="n">
+      <c r="AE25" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AF25" s="11" t="n">
+      <c r="AF25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AG25" s="11" t="n">
+      <c r="AG25" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AH25" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI25" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ25" s="8" t="inlineStr">
+      <c r="AH25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI25" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ25" s="1" t="inlineStr">
         <is>
           <t>Verified. The only clean sweep: 42/42 raw and strict, 34/34 answers, 8/8 declines, 0 over-refusals, 0 fabricated arguments, 0 schema errors, 1 tool error in 142 calls. Clears every question family. Worth noting it is not deterministic — 9 of 21 questions differed between repeats despite seed=42 and temperature=0 — but the variation never changed an outcome.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="11" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>5-5 std</t>
         </is>
       </c>
-      <c r="C26" s="11" t="inlineStr">
+      <c r="C26" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D26" s="11" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E26" s="11" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F26" s="11" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>gpt-5.5</t>
         </is>
       </c>
-      <c r="H26" s="11" t="inlineStr">
+      <c r="H26" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I26" s="11" t="inlineStr">
+      <c r="I26" s="3" t="inlineStr">
         <is>
           <t>runs-20260812-231900.jsonl</t>
         </is>
       </c>
-      <c r="J26" s="11" t="n">
+      <c r="J26" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K26" s="11" t="n">
+      <c r="K26" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="M26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" s="11" t="n">
+      <c r="M26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="n">
         <v>3.24</v>
       </c>
-      <c r="Q26" s="11" t="n">
+      <c r="Q26" s="3" t="n">
         <v>1.19</v>
       </c>
-      <c r="R26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="11" t="n">
+      <c r="R26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="n">
         <v>8285</v>
       </c>
-      <c r="T26" s="11" t="n">
+      <c r="T26" s="3" t="n">
         <v>93</v>
       </c>
-      <c r="U26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="11" t="n">
+      <c r="U26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA26" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB26" s="11" t="n">
+      <c r="AA26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AC26" s="11" t="n">
+      <c r="AC26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AD26" s="11" t="n">
+      <c r="AD26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE26" s="11" t="n">
+      <c r="AE26" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AF26" s="11" t="n">
+      <c r="AF26" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AG26" s="11" t="n">
+      <c r="AG26" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AH26" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI26" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ26" s="8" t="inlineStr">
+      <c r="AH26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI26" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ26" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 36/42 — below both gpt-5.4 (42) and gpt-5.6-luna (37). Perfect at hops 3, 4 and 5 and 20/20 on chains; every one of its 6 losses is near-miss recovery (4/8) or refusal. Most stable GPT across repeats (only 2 of 21 questions varied).</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="11" t="inlineStr">
+    <row r="27" ht="75" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>5.6 sol</t>
         </is>
       </c>
-      <c r="C27" s="11" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E27" s="11" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F27" s="11" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>gpt-5.6-sol</t>
         </is>
       </c>
-      <c r="H27" s="11" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I27" s="11" t="inlineStr">
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>runs-20260813-100138.jsonl</t>
         </is>
       </c>
-      <c r="J27" s="11" t="n">
+      <c r="J27" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K27" s="11" t="n">
+      <c r="K27" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="3" t="n">
         <v>37</v>
       </c>
-      <c r="M27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" s="11" t="n">
+      <c r="M27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q27" s="11" t="n">
+      <c r="Q27" s="3" t="n">
         <v>1.28</v>
       </c>
-      <c r="R27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" s="11" t="n">
+      <c r="R27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3" t="n">
         <v>8139</v>
       </c>
-      <c r="T27" s="11" t="n">
+      <c r="T27" s="3" t="n">
         <v>95</v>
       </c>
-      <c r="U27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="11" t="n">
+      <c r="U27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AA27" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB27" s="11" t="n">
+      <c r="AA27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB27" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AC27" s="11" t="n">
+      <c r="AC27" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AD27" s="11" t="n">
+      <c r="AD27" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE27" s="11" t="n">
+      <c r="AE27" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AF27" s="11" t="n">
+      <c r="AF27" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AG27" s="11" t="n">
+      <c r="AG27" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AH27" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI27" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ27" s="8" t="inlineStr">
+      <c r="AH27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI27" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ27" s="1" t="inlineStr">
         <is>
           <t>Verified from its own log. Strict 37/42, no lucky passes — ties gpt-5.6-luna and beats gpt-5.5 (36), but still below gpt-5.4 (42). Perfect on chains (20/20), fan-out (4/4), truncation (2/2) and at every hop depth above 2; all 5 losses are near-miss recovery (4/8) or refusal. Zero fabricated arguments, zero schema errors, zero tool errors, zero repeats across 142 calls. 327s.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="11" t="inlineStr">
+    <row r="28" ht="90" customHeight="1">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>5.6 terra</t>
         </is>
       </c>
-      <c r="C28" s="11" t="inlineStr">
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="D28" s="11" t="inlineStr">
+      <c r="D28" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="F28" s="11" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>gpt-5.6-terra</t>
         </is>
       </c>
-      <c r="H28" s="11" t="inlineStr">
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="I28" s="11" t="inlineStr">
+      <c r="I28" s="3" t="inlineStr">
         <is>
           <t>runs-20260813-100722.jsonl</t>
         </is>
       </c>
-      <c r="J28" s="11" t="n">
+      <c r="J28" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="K28" s="11" t="n">
+      <c r="K28" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="3" t="n">
         <v>34</v>
       </c>
-      <c r="M28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" s="11" t="n">
+      <c r="M28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3" t="n">
         <v>2.95</v>
       </c>
-      <c r="Q28" s="11" t="n">
+      <c r="Q28" s="3" t="n">
         <v>1.22</v>
       </c>
-      <c r="R28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" s="11" t="n">
+      <c r="R28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3" t="n">
         <v>7642</v>
       </c>
-      <c r="T28" s="11" t="n">
+      <c r="T28" s="3" t="n">
         <v>83</v>
       </c>
-      <c r="U28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" s="11" t="n">
+      <c r="U28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA28" s="11" t="n">
+      <c r="AA28" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AB28" s="11" t="n">
+      <c r="AB28" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC28" s="11" t="n">
+      <c r="AC28" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AD28" s="11" t="n">
+      <c r="AD28" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE28" s="11" t="n">
+      <c r="AE28" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AF28" s="11" t="n">
+      <c r="AF28" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AG28" s="11" t="n">
+      <c r="AG28" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AH28" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI28" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ28" s="8" t="inlineStr">
+      <c r="AH28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI28" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ28" s="1" t="inlineStr">
         <is>
           <t>Verified from its own log. Strict 34/42 — the weakest of the three 5.6 variants (luna 37, sol 37) and below gpt-5.5 (36). Identical shape to its siblings: 20/20 chains, 4/4 fan-out, 2/2 truncation, perfect at hops 3-5, with every loss in near-miss recovery (2/8, the worst of the 5.x line) or refusal (6/8, 6 over-refusals). Zero fabricated arguments, zero schema errors, zero tool errors. Fastest of the pair at 210s and the leanest caller (2.95 calls/run).</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="G29" s="10" t="n"/>
+      <c r="G29" s="2" t="n"/>
     </row>
     <row r="30">
-      <c r="G30" s="11" t="n"/>
-      <c r="H30" s="11" t="n"/>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
-      <c r="G31" s="10" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="H31" s="11" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="3" t="inlineStr">
         <is>
           <t>gemma4:e2b</t>
         </is>
       </c>
-      <c r="H32" s="11" t="inlineStr">
+      <c r="H32" s="3" t="inlineStr">
         <is>
           <t>Used less memory than expected</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="3" t="inlineStr">
         <is>
           <t>gemma4:e4b</t>
         </is>
       </c>
-      <c r="H33" s="11" t="inlineStr">
+      <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Used less memory than expected</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>deepseek-r1:8b</t>
         </is>
       </c>
-      <c r="H34" s="11" t="inlineStr">
+      <c r="H34" s="3" t="inlineStr">
         <is>
           <t>Did thinking even though turned off</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="3" t="inlineStr">
         <is>
           <t>gpt-4o</t>
         </is>
       </c>
-      <c r="H35" s="11" t="inlineStr">
+      <c r="H35" s="3" t="inlineStr">
         <is>
           <t>Hit major rate limiting</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="3" t="inlineStr">
         <is>
           <t>deepseek-r1:8b</t>
         </is>
       </c>
-      <c r="H36" s="11" t="inlineStr">
+      <c r="H36" s="3" t="inlineStr">
         <is>
           <t>Retested at MaxOutputTokens 6000: still zero tool calls. Reclassified as a hard fail alongside granite3.3:8b and command-r7b — all wire-confirmed to receive 25 tool definitions and call none.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="3" t="inlineStr">
         <is>
           <t>phi4-mini</t>
         </is>
       </c>
-      <c r="H37" s="11" t="inlineStr">
+      <c r="H37" s="3" t="inlineStr">
         <is>
           <t>Zero tool calls, but emits well-formed tool-call JSON into the content channel without the &lt;|tool_call|&gt; delimiter its own template requires. Run at Repeats=1 / cap 6000, so 21 runs not 42.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="G38" s="11" t="n"/>
-      <c r="H38" s="11" t="n"/>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>Validation</t>
-        </is>
-      </c>
-      <c r="H39" s="11" t="n"/>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>qwen2.5:1.5b / mistral</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>Both were run after the fact rather than left as unverified 'hard fail' labels. mistral's label was confirmed (zero tool calls, wire-checked). qwen2.5:1.5b's was WRONG — it does call tools, 15 times across 42 runs. Same config as the rest of Sheet1.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="H40" s="11" t="inlineStr">
+      <c r="H40" s="3" t="inlineStr">
         <is>
           <t>All rows recomputed from the regraded JSONL (grader deterministic-substring-v3). One transcription error found and corrected: ref /8 for qwen2.5:7b, 5 -&gt; 8.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="H41" s="11" t="inlineStr">
+      <c r="H41" s="3" t="inlineStr">
         <is>
           <t>v3 changes: fabricated arguments split into invented row id vs invented search term, and an answer truncated by the token cap can no longer be graded as a refusal. Regrading all 968 runs produced 0 correct/declined flips — both changes are additive.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="H42" s="11" t="inlineStr">
+      <c r="H42" s="3" t="inlineStr">
         <is>
           <t>Caveat on the hop columns: the v2 near-miss and truncation questions all sit at hop 2, so 'hop 2 ans' measures search recovery as much as depth. Chain-only scores are in RESULTS-ANALYSIS.md.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="H43" s="11" t="inlineStr">
+      <c r="H43" s="3" t="inlineStr">
         <is>
           <t>Determinism check: 10 eval invocations of nearmiss-film-rate on qwen3.5:9b (20 runs) gave 19 bit-identical and 1 divergent only in the final free-text iteration; load_duration flat 238-324ms throughout, so not a model reload.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="H44" s="11" t="inlineStr">
+      <c r="H44" s="3" t="inlineStr">
         <is>
           <t>gpt-5.6-sol and gpt-5.6-terra were run later on the same config and graded live at v3. One config difference from the earlier GPT rows: the OpenAI client now retries 429/5xx with backoff, which affects resilience, not output.</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="H45" s="11" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>phi4-mini (row 21) and the deepseek-r1 retest used Repeats=1 and MaxOutputTokens 6000. Their run COUNTS are therefore out of 21, not 42; rates are comparable, totals are not.</t>
         </is>
@@ -4020,4 +4168,586 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" min="15" max="15"/>
+    <col width="8" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>CONTROL SURFACE — NOT A CAPABILITY RANKING. Two tools (get_schema, execute_sql) and the 10 linear chain questions only. Text-to-SQL has far more training data behind it than agentic tool composition, so a model scoring higher here shows THE TASK CHANGED, not that it is a better agent. Read the Delta against the same model's chain score on standard+desc, never the absolute number.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Same config as the main sweep: seed 42, temperature 0, thinking off, MaxOutputTokens 2500, MaxIterations 10, repeats 2. Ollama keep-alive 5m, num_parallel 1, max_loaded_models 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Output file</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Chain (main) /20</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Correct /20</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Questions /10</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Calls p/run</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>Iters p/run</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>SQL calls</t>
+        </is>
+      </c>
+      <c r="K7" s="9" t="inlineStr">
+        <is>
+          <t>SQL errors</t>
+        </is>
+      </c>
+      <c r="L7" s="9" t="inlineStr">
+        <is>
+          <t>SQL err p/run</t>
+        </is>
+      </c>
+      <c r="M7" s="9" t="inlineStr">
+        <is>
+          <t>get_schema calls</t>
+        </is>
+      </c>
+      <c r="N7" s="10" t="inlineStr">
+        <is>
+          <t>Read schema first</t>
+        </is>
+      </c>
+      <c r="O7" s="9" t="inlineStr">
+        <is>
+          <t>No tool call</t>
+        </is>
+      </c>
+      <c r="P7" s="9" t="inlineStr">
+        <is>
+          <t>Cap hits</t>
+        </is>
+      </c>
+      <c r="Q7" s="9" t="inlineStr">
+        <is>
+          <t>Elapsed (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>granite3.3:8b</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260813-173541.jsonl</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>command-r7b</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260813-173722.jsonl</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260813-174525.jsonl</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
+        <is>
+          <t>0/20</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>mistral-nemo:12b</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260813-173751.jsonl</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="N11" s="11" t="inlineStr">
+        <is>
+          <t>0/14</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>gemma4:e4b</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260813-174007.jsonl</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N12" s="11" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>qwen3.5:4b</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260813-174156.jsonl</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="N13" s="11" t="inlineStr">
+        <is>
+          <t>20/20</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>WHAT IT SHOWS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>The constraint is not what causes the failures. Handing the four failing models a generic SQL tool moved the aggregate by 2 runs out of 80. If the no-shortcuts surface were manufacturing failure rather than measuring it, removing it should have lifted them. It did not.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>granite3.3:8b and command-r7b made ZERO tool calls here too, exactly as on the main surface. A shortcut is still a tool call, so nothing about the surface can fix a model that will not use the tool channel. (Predicted.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>llama3.2 and mistral-nemo did NOT improve as predicted. Both sit at exactly 1.00 calls and 2.00 iterations per run on BOTH surfaces: one call, then answer, whatever it returned. The surface changed; the shape of the failure did not. mistral-nemo's +2 is two blind guesses that happened to be right.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>'Read schema first' (highlighted) separates the two groups perfectly, with no overlap. The models that skip it invent table names that do not exist (films, actors, customers) — the main sweep's fabricated-argument instinct in a new form. The failing behaviour is not 'cannot chain', it is 'will not check'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Errors only help a model that reads them. gemma4 hit 18 SQL errors in 48 calls and still scored 18/20 because it iterates; llama3.2 hit 20 in 20 and scored 0 because it never issues a second query.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Control held: qwen3.5:4b 20-&gt;20, gemma4:e4b 18-&gt;18. gemma4's flat score hides a moved failure — hop5-title-2025-renter on the main surface, hop4-inventory-store-city here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>CAVEATS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>The brief named five models and listed six; all six were run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>'llama3.2:3b' is not a pulled Ollama tag — the first attempt 404'd on every run and was re-run against 'llama3.2', the tag the main sweep used. The errored file was discarded, not reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>navigation_complete, required_tools, hop depth and argument provenance are omitted from these runs' JSONL entirely rather than recorded as zero: with one generic tool they are undefined, and zero reads as a failure.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:Q3"/>
+    <mergeCell ref="A22:Q22"/>
+    <mergeCell ref="A17:Q17"/>
+    <mergeCell ref="A18:Q18"/>
+    <mergeCell ref="A27:Q27"/>
+    <mergeCell ref="A21:Q21"/>
+    <mergeCell ref="A20:Q20"/>
+    <mergeCell ref="A24:Q24"/>
+    <mergeCell ref="A16:Q16"/>
+    <mergeCell ref="A26:Q26"/>
+    <mergeCell ref="A25:Q25"/>
+    <mergeCell ref="A19:Q19"/>
+    <mergeCell ref="A5:Q5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/LlmMoveiAgentResults.xlsx
+++ b/LlmMoveiAgentResults.xlsx
@@ -75,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -99,6 +99,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -186,6 +189,13 @@
         <t>Strict score, computed from the logs (EvalSummary.NavigatedCorrect).
 Correct AND, where the question requires traversal, having actually reached every required tool.
 Drops passes the model landed on by luck: llama3.1 calling get_film(1) without searching and being right because film 1 happens to be English. A decline needs no traversal, so it is exempt.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Schema-enumerated ids: a contiguous sweep of at least 4 values inside the range the tool advertises in its own schema.
+Counted APART from Fab. ID, not as part of it. The grounding corpus is the question plus prior tool results and excludes the tool declarations, so a model that reads 'Category identifier, 1 to 16' off get_category and walks 1..16 scored as fabricating all sixteen. Every one of those calls succeeded.
+Deliberately narrow: 68% of all fabricated ids in the corpus are in range, and most are single blind guesses. Contiguity is the discriminator — llama3.1, the worst fabricator at 306, has none.</t>
       </text>
     </comment>
     <comment ref="Z4" authorId="0" shapeId="0">
@@ -518,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ45"/>
+  <dimension ref="A1:AK45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -545,6 +555,7 @@
     <col width="7.42578125" customWidth="1" min="26" max="26"/>
     <col width="8.42578125" customWidth="1" min="27" max="27"/>
     <col width="78" customWidth="1" min="36" max="36"/>
+    <col width="78" customWidth="1" min="37" max="37"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -653,77 +664,82 @@
           <t>Fab. ID</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="V1" s="13" t="inlineStr">
+        <is>
+          <t>Sch. Enum</t>
+        </is>
+      </c>
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>Fab. Term</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>call id as arg</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>type m/m</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>schema err.</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>ref  /8</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>over-ref</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>hop 2 ans</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>hop 2 nav</t>
         </is>
       </c>
-      <c r="AD1" s="4" t="inlineStr">
+      <c r="AE1" s="4" t="inlineStr">
         <is>
           <t>hop 3 ans</t>
         </is>
       </c>
-      <c r="AE1" s="4" t="inlineStr">
+      <c r="AF1" s="4" t="inlineStr">
         <is>
           <t>hop 3 nav</t>
         </is>
       </c>
-      <c r="AF1" s="4" t="inlineStr">
+      <c r="AG1" s="4" t="inlineStr">
         <is>
           <t>hop 4 ans</t>
         </is>
       </c>
-      <c r="AG1" s="4" t="inlineStr">
+      <c r="AH1" s="4" t="inlineStr">
         <is>
           <t>hop 4 nav</t>
         </is>
       </c>
-      <c r="AH1" s="4" t="inlineStr">
+      <c r="AI1" s="4" t="inlineStr">
         <is>
           <t>hop 5 ans</t>
         </is>
       </c>
-      <c r="AI1" s="4" t="inlineStr">
+      <c r="AJ1" s="4" t="inlineStr">
         <is>
           <t>hop 5 nav</t>
         </is>
       </c>
-      <c r="AJ1" s="4" t="inlineStr">
+      <c r="AK1" s="4" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -764,7 +780,7 @@
       </c>
       <c r="I2" s="12" t="inlineStr">
         <is>
-          <t>runs-20260814-122314.jsonl</t>
+          <t>runs-20260814-134116.jsonl</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
@@ -786,7 +802,7 @@
         <v>6</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>1</v>
@@ -795,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="S2" s="3" t="n">
-        <v>3263</v>
+        <v>3384</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>185</v>
+        <v>250</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>5</v>
@@ -810,29 +826,29 @@
         <v>0</v>
       </c>
       <c r="X2" s="3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="Z2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="AB2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AD2" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AE2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AF2" s="3" t="n">
         <v>0</v>
       </c>
@@ -845,9 +861,12 @@
       <c r="AI2" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" s="1" t="inlineStr">
-        <is>
-          <t>RUN AFTER THE FACT — the 'didn't call tools' label was WRONG and only running it showed that. It made 15 tool calls across 42 runs, 11 of which succeeded; 28 of 42 runs made none. Strict 0/42: both of its two 'correct' are nearmiss-film-language answered with ZERO tool calls, guessing 'English' from priors and appending the non-sequitur 'ERROR: The query returned no results.' — the expected answer happens to be English, so substring matching passed it. 10 of 42 runs print the tool DECLARATION schema back as text ('{"type": "function", "function": {search...'), i.e. it echoes the shape it was offered rather than issuing a call. 6 empty answers, 9 fabricated arguments (5 invented ids), 3 schema errors, 0/8 declines. Genuinely answered 0 of 34.</t>
+      <c r="AJ2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="1" t="inlineStr">
+        <is>
+          <t>RUN AFTER THE FACT — the 'didn't call tools' label was WRONG and only running it showed that. It makes 17 tool calls across 42 runs; 28 of 42 runs make none. Strict 0/42: both of its two 'correct' are nearmiss-film-language answered with ZERO tool calls, guessing 'English' from priors and appending the non-sequitur 'ERROR: The query returned no results.' — the expected answer happens to be English, so substring matching passed it. 10 of 42 runs print the tool DECLARATION schema back as text ('{"type": "function", "function": {search...'), echoing the shape it was offered rather than issuing a call. It is not a tool-channel failure like mistral; it uses the channel, rarely, and then cannot chain. 6 empty answers, 5 invented ids, 5 schema errors, 0/8 declines, genuinely answered 0 of 34. NOTE ON PROVENANCE: an earlier sweep of this model (runs-20260814-122314.jsonl) ran while Agent:NormaliseToolCallIds was off and is not comparable with the rest of Sheet1; it is kept as the evidence that call_id_as_argument_count is blind when ids are not normalised (0 there, 3 here, same behaviour). This row is the normalised re-run.</t>
         </is>
       </c>
     </row>
@@ -921,32 +940,32 @@
         <v>67</v>
       </c>
       <c r="V3" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="W3" s="3" t="n">
+      <c r="X3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="X3" s="3" t="n">
+      <c r="Y3" s="3" t="n">
         <v>17</v>
       </c>
-      <c r="Y3" s="3" t="n">
+      <c r="Z3" s="3" t="n">
         <v>51</v>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AA3" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AB3" s="3" t="n">
+      <c r="AC3" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AC3" s="3" t="n">
+      <c r="AD3" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AD3" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AE3" s="3" t="n">
         <v>0</v>
       </c>
@@ -962,7 +981,10 @@
       <c r="AI3" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" s="1" t="inlineStr">
+      <c r="AJ3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 10/42 — 2 passes never reached the required tools (guessed get_film(123) on nearmiss-film-rate without searching). Worst argument discipline in the set, and it is the bad kind: 67 of its 78 fabricated arguments are invented row ids, not search terms. 51 schema errors, 53% of all tool calls errored, 34 blocked repeats. Sends literal placeholders as ids ('result of previous search_film call', '{{result.store_id}}'). Nothing above hop 2.</t>
         </is>
@@ -1035,10 +1057,10 @@
         <v>143</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W4" s="3" t="n">
         <v>0</v>
@@ -1047,41 +1069,44 @@
         <v>0</v>
       </c>
       <c r="Y4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="Z4" s="7" t="n">
-        <v>8</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AB4" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC4" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AC4" s="3" t="n">
+      <c r="AD4" s="3" t="n">
         <v>7</v>
-      </c>
-      <c r="AD4" s="3" t="n">
-        <v>6</v>
       </c>
       <c r="AE4" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AF4" s="3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG4" s="3" t="n">
         <v>5</v>
       </c>
       <c r="AH4" s="3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" s="1" t="inlineStr">
-        <is>
-          <t>CORRECTION applied: 'ref /8' was 5, should be 8 — the JSONL records 8/8 correctly declined. Every other figure verified. Strict 24/42, no lucky passes. Solid mid-chain (hop3 6/10, hop4 5/6) but 0/4 at hop5 and 1/8 on near-miss recovery. All 18 fabricated arguments are invented ids. 2 cap hits.</t>
+      <c r="AJ4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="1" t="inlineStr">
+        <is>
+          <t>CORRECTION applied: 'ref /8' was 5, should be 8 — the JSONL records 8/8 correctly declined. Every other figure verified. Strict 24/42, no lucky passes. Solid mid-chain (hop3 6/10, hop4 5/6) but 0/4 at hop5 and 1/8 on near-miss recovery. Its 18 flagged arguments split 8 invented ids and 10 schema-enumerated (a contiguous sweep of a range the tool advertises, counted apart from fabrication). 2 cap hits.</t>
         </is>
       </c>
     </row>
@@ -1172,36 +1197,39 @@
         <v>0</v>
       </c>
       <c r="Z5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA5" s="3" t="n">
+      <c r="AB5" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="AB5" s="3" t="n">
-        <v>8</v>
       </c>
       <c r="AC5" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE5" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG5" s="3" t="n">
         <v>4</v>
       </c>
       <c r="AH5" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AJ5" s="1" t="inlineStr">
+      <c r="AJ5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 29/42, no lucky passes. Zero fabricated arguments of either kind, zero schema errors, 1 error in 103 calls — the cleanest small local model. Perfect refusal (8/8) but 10 over-refusals. 0/8 on near-miss recovery: gives up after one NO ROWS instead of shortening the search term.</t>
         </is>
@@ -1282,11 +1310,11 @@
         <v>0</v>
       </c>
       <c r="V6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="W6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X6" s="3" t="n">
         <v>0</v>
       </c>
@@ -1294,25 +1322,25 @@
         <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AA6" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB6" s="3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AC6" s="3" t="n">
         <v>12</v>
       </c>
       <c r="AD6" s="3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AE6" s="3" t="n">
         <v>10</v>
       </c>
       <c r="AF6" s="3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AG6" s="3" t="n">
         <v>4</v>
@@ -1323,7 +1351,10 @@
       <c r="AI6" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ6" s="1" t="inlineStr">
+      <c r="AJ6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK6" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 32/42. Perfect 20/20 on pure dependency chains — equal to GPT-4o and gpt-5.4 on that axis, at 4B. 6/8 on near-miss recovery, beating every GPT-4o-class model. Fabrication is fully exonerated by the split: all 18 are invented SEARCH TERMS and zero are invented ids — that is hunting for entities that do not exist, not hallucinating rows. Never over-refuses (0) but rarely declines (2/8); burns iterations instead (8 cap hits, 28 blocked repeats). Bit-identical across repeats (a 20-run follow-up on qwen3.5:9b measured the qwen3.5 divergence rate at 1 in 20, confined to final-answer prose and flagged by a 12x latency outlier; tool calls never varied).</t>
         </is>
@@ -1396,14 +1427,14 @@
         <v>320</v>
       </c>
       <c r="U7" s="3" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="V7" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="W7" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="W7" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X7" s="3" t="n">
         <v>0</v>
       </c>
@@ -1411,38 +1442,41 @@
         <v>0</v>
       </c>
       <c r="Z7" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA7" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AB7" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC7" s="3" t="n">
         <v>14</v>
       </c>
       <c r="AD7" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE7" s="3" t="n">
         <v>10</v>
       </c>
       <c r="AF7" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG7" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AH7" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ7" s="1" t="inlineStr">
-        <is>
-          <t>Verified. Strict 38/42 — best non-GPT, and beats GPT-4o (31), GPT-4o-mini (28) and gpt-5.5 (36). Perfect on every answerable question: 34/34, incl. 20/20 chains, 8/8 near-miss, 4/4 fan-out, 4/4 hop5. All 4 losses are refusal cases it tried to answer; never over-refuses. Its 48 fabricated arguments split 34 id / 14 term, but 32 of the 34 ids are a sequential sweep of get_category(category_id=1..16) on decline-easy-category, using bounds the tool itself advertises — exhaustive enumeration, not hallucination. Only 2 loose invented ids in 42 runs. Slowest local model at 10.2s/run.</t>
+      <c r="AJ7" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK7" s="1" t="inlineStr">
+        <is>
+          <t>Verified. Strict 38/42 — best non-GPT, and beats GPT-4o (31), GPT-4o-mini (28) and gpt-5.5 (36). Perfect on every answerable question: 34/34, incl. 20/20 chains, 8/8 near-miss, 4/4 fan-out, 4/4 hop5. All 4 losses are refusal cases it tried to answer; never over-refuses. Its 48 flagged arguments now split 2 invented ids, 14 invented search terms and 32 SCHEMA-ENUMERATED — a sequential sweep of get_category(category_id=1..16) on decline-easy-category, using bounds the tool itself advertises, every call successful. Two loose invented ids in 42 runs, the cleanest in the set after the zero-fabrication models. Slowest local model at 10.2s/run.</t>
         </is>
       </c>
     </row>
@@ -1516,48 +1550,51 @@
         <v>8</v>
       </c>
       <c r="V8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="W8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X8" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z8" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AA8" s="3" t="n">
         <v>4</v>
       </c>
       <c r="AB8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AC8" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AC8" s="3" t="n">
+      <c r="AD8" s="3" t="n">
         <v>12</v>
-      </c>
-      <c r="AD8" s="3" t="n">
-        <v>6</v>
       </c>
       <c r="AE8" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AF8" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AG8" s="3" t="n">
         <v>4</v>
       </c>
       <c r="AH8" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AJ8" s="1" t="inlineStr">
+      <c r="AK8" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 20/42. Chain 14/20 but 0/8 near-miss and 0/4 fan-out. 24 fabricated arguments lean toward search terms (16 term / 8 id). 4 cap hits, 16 blocked repeats — loops on failed searches with case variants ('SteepPUNK', 'Steeppunk'). Deterministic across repeats.</t>
         </is>
@@ -1630,14 +1667,14 @@
         <v>431</v>
       </c>
       <c r="U9" s="3" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="V9" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="W9" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="W9" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X9" s="3" t="n">
         <v>0</v>
       </c>
@@ -1651,32 +1688,35 @@
         <v>0</v>
       </c>
       <c r="AB9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AC9" s="3" t="n">
+      <c r="AD9" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="AD9" s="3" t="n">
+      <c r="AE9" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="AE9" s="3" t="n">
+      <c r="AF9" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AF9" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AG9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH9" s="3" t="n">
         <v>6</v>
-      </c>
-      <c r="AH9" s="3" t="n">
-        <v>2</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ9" s="1" t="inlineStr">
-        <is>
-          <t>Verified. Strict 20/42 (2 lucky). Q4 against the Q8 build of the same 2B: raw score +2, but cap hits 4x worse (16 vs 4) and fabricated arguments 3.7x (88 vs 24) — and the split shows the damage is id-side, 66 invented ids against the Q8 build's 8. Called get_film 114 times brute-forcing ids. Never declines (0/8), never over-refuses (0). Quantisation cost shows up as loop control, not knowledge.</t>
+      <c r="AJ9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK9" s="1" t="inlineStr">
+        <is>
+          <t>Verified. Strict 20/42 (2 lucky). Q4 against the Q8 build of the same 2B: raw score +2, but cap hits 4x worse (16 vs 4) and fabricated arguments 3.7x (88 vs 24) — and the split shows the damage is id-side: 30 invented ids and 36 schema-enumerated against the Q8 build's 8 invented and none swept. Called get_film 114 times brute-forcing ids. Never declines (0/8), never over-refuses (0). Quantisation cost shows up as loop control, not knowledge.</t>
         </is>
       </c>
     </row>
@@ -1755,38 +1795,38 @@
         <v>138</v>
       </c>
       <c r="V10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="W10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="Y10" s="3" t="n">
+      <c r="Z10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="Z10" s="3" t="n">
+      <c r="AA10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AA10" s="3" t="n">
+      <c r="AB10" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="AB10" s="3" t="n">
+      <c r="AC10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AC10" s="3" t="n">
+      <c r="AD10" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AD10" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AE10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AF10" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG10" s="3" t="n">
         <v>0</v>
       </c>
@@ -1796,7 +1836,10 @@
       <c r="AI10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" s="1" t="inlineStr">
+      <c r="AJ10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="1" t="inlineStr">
         <is>
           <t>Verified, but the raw 9 is misleading — strict 4/42, the biggest inflation in the set. 5 of the 9 passes never reached the required tools: it calls get_film(film_id=1), and film 1 happens to be English with rental_duration 6, which are the expected answers to two near-miss questions. Genuinely answered 1 of 34. The worst fabricator in the sweep and unambiguously so: 138 of 145 are invented row ids with no enumeration pattern behind them. 96 errored calls (58%), 65 blocked repeats. Fires ~4 calls in one iteration then stops — no read-then-plan loop. 16 over-refusals.</t>
         </is>
@@ -1877,25 +1920,25 @@
         <v>20</v>
       </c>
       <c r="V11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="W11" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="Y11" s="3" t="n">
+      <c r="Z11" s="3" t="n">
         <v>18</v>
       </c>
-      <c r="Z11" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AA11" s="3" t="n">
         <v>4</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AC11" s="3" t="n">
         <v>0</v>
@@ -1918,7 +1961,10 @@
       <c r="AI11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" s="1" t="inlineStr">
+      <c r="AJ11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 4/42, all 4 refusals — answered 0 of 34. Exactly one tool call per run, then stops. 57% of calls errored: passes titles where ids are required ('AGENT TRUMAN' as film_id) and wrong parameter names (title_contains to get_film). Never chains.</t>
         </is>
@@ -1999,26 +2045,26 @@
         <v>7</v>
       </c>
       <c r="V12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="W12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="X12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Y12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="Z12" s="3" t="n">
+      <c r="AA12" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA12" s="3" t="n">
+      <c r="AB12" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="AB12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC12" s="3" t="n">
         <v>0</v>
       </c>
@@ -2026,11 +2072,11 @@
         <v>0</v>
       </c>
       <c r="AE12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AF12" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AG12" s="3" t="n">
         <v>0</v>
       </c>
@@ -2040,7 +2086,10 @@
       <c r="AI12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ12" s="1" t="inlineStr">
+      <c r="AJ12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 6/42, all 6 refusals — answered 0 of 34, despite being the largest local model tested. 1.05 calls/run, 2.0 iterations/run: one call, then it answers. Only 2 errored calls, so it is not malformed — it simply never takes a second hop. 12 over-refusals.</t>
         </is>
@@ -2133,14 +2182,14 @@
         <v>0</v>
       </c>
       <c r="Z13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AA13" s="3" t="n">
+      <c r="AB13" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AB13" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC13" s="3" t="n">
         <v>0</v>
       </c>
@@ -2162,7 +2211,10 @@
       <c r="AI13" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ13" s="1" t="inlineStr">
+      <c r="AJ13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="1" t="inlineStr">
         <is>
           <t>RUN AFTER THE FACT — label CONFIRMED. Zero tool calls in all 42 runs, wire-checked: 25 tool definitions sent in correct Ollama format, no tool_calls field in the response. Belongs with granite3.3:8b, command-r7b, deepseek-r1:8b and phi4-mini. Its failure mode is its own though: 31 of 42 runs write pseudo-code function calls inside markdown fences — ```search_film(title_contains="alamo videotape")``` — then continue as if they had run, prefaced with 'Assuming...'. Both of its 2 correct are genuine refusals on unreachable-total-film-count ('there's no tool that directly...'), so strict 2/42 but genuinely answered 0 of 34. Declares the 'tools' capability and its template handles them.</t>
         </is>
@@ -2255,19 +2307,19 @@
         <v>0</v>
       </c>
       <c r="Z14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA14" s="3" t="n">
+      <c r="AB14" s="3" t="n">
         <v>10</v>
-      </c>
-      <c r="AB14" s="3" t="n">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AD14" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AE14" s="3" t="n">
         <v>4</v>
@@ -2276,7 +2328,7 @@
         <v>4</v>
       </c>
       <c r="AG14" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AH14" s="3" t="n">
         <v>2</v>
@@ -2284,7 +2336,10 @@
       <c r="AI14" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ14" s="1" t="inlineStr">
+      <c r="AJ14" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK14" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 24/42 (2 lucky on hop4-customer-country). Zero fabricated arguments of either kind, zero schema errors, zero tool errors across 102 calls — the cleanest caller in the set. Perfect refusal 8/8 but 10 over-refusals. A second full run (runs-20260812-214734.jsonl) scored an identical 26/42 with the same per-hop split, so this result is reproducible.</t>
         </is>
@@ -2377,23 +2432,23 @@
         <v>0</v>
       </c>
       <c r="Z15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AA15" s="3" t="n">
+      <c r="AB15" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="AB15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC15" s="3" t="n">
         <v>0</v>
       </c>
       <c r="AD15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AE15" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AF15" s="3" t="n">
         <v>0</v>
       </c>
@@ -2406,7 +2461,10 @@
       <c r="AI15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" s="1" t="inlineStr">
+      <c r="AJ15" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls in all 42 runs, wire-confirmed. Strict 3/42 and answered 0 of 34. It prints tool calls as prose ('&lt;|tool call{...}|&gt;' and json blocks) in 17 runs instead of using the tool-call channel. Re-ran with wire capture: 25 tool definitions were sent correctly and it described them accurately, then called none — model behaviour, not a harness fault. Its 4 'correct' include 2 grader false positives. The numbers here are real but should be read as a hard fail, not a low score.</t>
         </is>
@@ -2499,14 +2557,14 @@
         <v>0</v>
       </c>
       <c r="Z16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA16" s="3" t="n">
+      <c r="AB16" s="3" t="n">
         <v>33</v>
       </c>
-      <c r="AB16" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC16" s="3" t="n">
         <v>0</v>
       </c>
@@ -2528,7 +2586,10 @@
       <c r="AI16" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ16" s="1" t="inlineStr">
+      <c r="AJ16" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls in all 42 runs, wire-confirmed (25 tools sent, none called). Strict 8/42, but all 8 are refusals; it answered 0 of 34 and refused 33 of 34 answerable questions ('I don't have access to information about...'). Its perfect 8/8 refusal score is the clearest demonstration here that refusal accuracy is meaningless without the over-refusal denominator.</t>
         </is>
@@ -2621,13 +2682,13 @@
         <v>0</v>
       </c>
       <c r="Z17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA17" s="3" t="n">
+      <c r="AB17" s="3" t="n">
         <v>12</v>
-      </c>
-      <c r="AB17" s="3" t="n">
-        <v>8</v>
       </c>
       <c r="AC17" s="3" t="n">
         <v>8</v>
@@ -2639,18 +2700,21 @@
         <v>8</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG17" s="3" t="n">
         <v>4</v>
       </c>
       <c r="AH17" s="3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" s="1" t="inlineStr">
+      <c r="AJ17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 28/42, no lucky passes. Zero fabricated arguments, zero schema errors, zero tool errors. Beats its larger sibling e4b (26). Chain 18/20 but 0/8 near-miss and 0/4 fan-out — it fails only where recovery or breadth is needed. 12 over-refusals is the price of its 8/8 refusal. The 2 empty answers are clean stops after one call, not truncation.</t>
         </is>
@@ -2738,10 +2802,10 @@
         <v>0</v>
       </c>
       <c r="Z18" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AB18" s="3" t="n">
         <v>8</v>
@@ -2756,18 +2820,21 @@
         <v>8</v>
       </c>
       <c r="AF18" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG18" s="3" t="n">
         <v>4</v>
       </c>
       <c r="AH18" s="3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AJ18" s="1" t="inlineStr">
+      <c r="AJ18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK18" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 26/42. Scores below the smaller e2b (28): more answers right (22 vs 20) but fewer refusals (4/8 vs 8/8). Same clean discipline — 0 fabricated, 0 schema errors, 0 tool errors. Both empty answers are on nearmiss-word-order and identical across repeats.</t>
         </is>
@@ -2851,32 +2918,32 @@
         <v>0</v>
       </c>
       <c r="W19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="X19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Y19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="Z19" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AA19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB19" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="AB19" s="3" t="n">
+      <c r="AC19" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="AC19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AD19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AE19" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AF19" s="3" t="n">
         <v>0</v>
       </c>
@@ -2889,7 +2956,10 @@
       <c r="AI19" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ19" s="1" t="inlineStr">
+      <c r="AJ19" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 4/42 (3 lucky) — answered 0 of 34. Leaks the harness's own tool-call envelope back as arguments, sending {'Arguments':{...},'CallId':'call_2','FunctionName':'get_staff'} as the argument object. That is why its 21 fabricated arguments split to only 11 id and 0 term: the other 10 are on parameter names no tool declares, which is also the whole of its schema-error count. 13 of 42 runs made no tool call at all.</t>
         </is>
@@ -2982,14 +3052,14 @@
         <v>0</v>
       </c>
       <c r="Z20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AA20" s="3" t="n">
+      <c r="AB20" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="AB20" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3" t="n">
         <v>0</v>
       </c>
@@ -3011,7 +3081,10 @@
       <c r="AI20" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" s="1" t="inlineStr">
+      <c r="AJ20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls, wire-confirmed, at BOTH token caps. Strict 1/42 and its true score is 0: the single point is a grader artefact (a complete sentence containing the conditional 'I cannot proceed further without guessing', inside a plan it never executed, read as a refusal). RETEST: re-run at MaxOutputTokens 6000 (runs-20260813-162941.jsonl, 21 questions x 1 repeat) to test whether the 2500 cap was the cause. It was not. Truncation fell from 31/42 to 3/21 and empty answers from 31 to 3, so the cap was a real constraint — but tool calls stayed at ZERO and the score did not move. Every run is one iteration: no tool call means nothing to feed back. It writes an essay about calling tools instead (309,720 chars of reasoning vs 10,186 of answer) naming tools that mostly do not exist (search_film_by_title, get_rental_film_id). Wire at 6000: 25 tools sent, no tool_calls field, 11,497 chars of 'thinking', content ending '&lt;tool&gt;search_film_by_title&lt;/tool&gt;' — its own invented pseudo-syntax in the content channel. Also ignores Agent:Thinking=false entirely (reasoning in every iteration). Costs 50% more wall clock at the higher cap for an identical zero. The earlier 'untestable at this MaxOutputTokens' caveat is retired — the cap was hiding the failure, not causing it.</t>
         </is>
@@ -3104,13 +3177,13 @@
         <v>0</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AB21" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" s="3" t="n">
         <v>0</v>
@@ -3133,7 +3206,10 @@
       <c r="AI21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" s="1" t="inlineStr">
+      <c r="AJ21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="1" t="inlineStr">
         <is>
           <t>HARD FAIL — zero tool calls in all 21 runs, wire-confirmed. True score 0/21: the single 'correct' is the same planning-monologue false positive as deepseek-r1. NOTE THE DIFFERENT CONFIG: Repeats=1 (21 runs, not 42) and MaxOutputTokens 6000, so the counts here are not directly comparable with the rows above; the rates are. Distinct from the other zero-call failures and the closest call of the four: it emits STRUCTURALLY CORRECT tool-call JSON — [{"name": "get_film", "arguments": {"film_id": 1}}] — with real tool and parameter names, but into the content channel (15 of 21 runs). Checked properly because that shape suggests a rig fault: /api/show reports phi4-mini declares the 'tools' capability and its template does handle them, rendering tools into &lt;|tool|&gt;...&lt;|/tool|&gt; and expecting calls back wrapped as &lt;|tool_call|&gt;[...]&lt;|/tool_call|&gt;. Wire capture: 25 tools sent, no tool_calls field in the response, and the content carries the bare JSON array with NO &lt;|tool_call|&gt; delimiter. So the model omits the delimiter its own chat template requires and Ollama cannot parse the payload — a model failure, but one pair of tags away from working. Two aggravating factors: it also hallucinates the RESULTS, roleplaying whole conversations with invented rows (invents the city 'Springfield', invents actor ids [1,2,3] then concludes '3 actors'), and its text-format calls are frequently malformed anyway ({"arguments"} as a second object rather than a key; "parameters" instead of "arguments"). Invents tools that do not exist (search_rental, search_inventory_item). Fast and cheap at 113 output tokens and 2.0s per run, which buys nothing.</t>
         </is>
@@ -3234,10 +3310,10 @@
         <v>0</v>
       </c>
       <c r="Z22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="3" t="n">
         <v>7</v>
-      </c>
-      <c r="AA22" s="3" t="n">
-        <v>8</v>
       </c>
       <c r="AB22" s="3" t="n">
         <v>8</v>
@@ -3252,7 +3328,7 @@
         <v>8</v>
       </c>
       <c r="AF22" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG22" s="3" t="n">
         <v>4</v>
@@ -3263,7 +3339,10 @@
       <c r="AI22" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ22" s="1" t="inlineStr">
+      <c r="AJ22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK22" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 31/42. Perfect 20/20 on dependency chains and 4/4 at hop 5, but 0/8 on near-miss recovery — the one axis where 4B local models clearly beat it (qwen3.5:4b 6/8, 9b 8/8). Zero fabricated arguments. The first attempt at this sweep (runs-20260812-224854.jsonl) errored 42/42 on rate limiting; this file is the clean re-run. Still the slowest GPT at 545s vs ~150s, consistent with retry backoff.</t>
         </is>
@@ -3359,10 +3438,10 @@
         <v>0</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA23" s="3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AB23" s="3" t="n">
         <v>8</v>
@@ -3377,7 +3456,7 @@
         <v>8</v>
       </c>
       <c r="AF23" s="3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="AG23" s="3" t="n">
         <v>4</v>
@@ -3388,7 +3467,10 @@
       <c r="AI23" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ23" s="1" t="inlineStr">
+      <c r="AJ23" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK23" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 28/42. Same shape as gpt-4o on chains (20/20) and near-miss (0/8), losing ground only on refusal (4/8 vs 7/8). Fastest GPT run at 146s.</t>
         </is>
@@ -3484,36 +3566,39 @@
         <v>0</v>
       </c>
       <c r="Z24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA24" s="3" t="n">
+      <c r="AB24" s="3" t="n">
         <v>3</v>
-      </c>
-      <c r="AB24" s="3" t="n">
-        <v>11</v>
       </c>
       <c r="AC24" s="3" t="n">
         <v>11</v>
       </c>
       <c r="AD24" s="3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE24" s="3" t="n">
         <v>10</v>
       </c>
       <c r="AF24" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG24" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AH24" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ24" s="1" t="inlineStr">
+      <c r="AJ24" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK24" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 37/42. Chain 20/20, fan-out 4/4, near-miss 5/8. Loses 3 runs to over-refusal and both repeats of decline-easy-category. Second-best refusal calibration after gpt-5.4.</t>
         </is>
@@ -3609,36 +3694,39 @@
         <v>0</v>
       </c>
       <c r="Z25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="AA25" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="AB25" s="3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="3" t="n">
         <v>14</v>
       </c>
       <c r="AD25" s="3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AE25" s="3" t="n">
         <v>10</v>
       </c>
       <c r="AF25" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG25" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AH25" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ25" s="1" t="inlineStr">
+      <c r="AJ25" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK25" s="1" t="inlineStr">
         <is>
           <t>Verified. The only clean sweep: 42/42 raw and strict, 34/34 answers, 8/8 declines, 0 over-refusals, 0 fabricated arguments, 0 schema errors, 1 tool error in 142 calls. Clears every question family. Worth noting it is not deterministic — 9 of 21 questions differed between repeats despite seed=42 and temperature=0 — but the variation never changed an outcome.</t>
         </is>
@@ -3734,13 +3822,13 @@
         <v>0</v>
       </c>
       <c r="Z26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="3" t="n">
         <v>6</v>
       </c>
-      <c r="AA26" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AB26" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AC26" s="3" t="n">
         <v>10</v>
@@ -3752,18 +3840,21 @@
         <v>10</v>
       </c>
       <c r="AF26" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG26" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AH26" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ26" s="1" t="inlineStr">
+      <c r="AJ26" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK26" s="1" t="inlineStr">
         <is>
           <t>Verified. Strict 36/42 — below both gpt-5.4 (42) and gpt-5.6-luna (37). Perfect at hops 3, 4 and 5 and 20/20 on chains; every one of its 6 losses is near-miss recovery (4/8) or refusal. Most stable GPT across repeats (only 2 of 21 questions varied).</t>
         </is>
@@ -3859,13 +3950,13 @@
         <v>0</v>
       </c>
       <c r="Z27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="AA27" s="3" t="n">
-        <v>4</v>
-      </c>
       <c r="AB27" s="3" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AC27" s="3" t="n">
         <v>10</v>
@@ -3877,18 +3968,21 @@
         <v>10</v>
       </c>
       <c r="AF27" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG27" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AH27" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ27" s="1" t="inlineStr">
+      <c r="AJ27" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK27" s="1" t="inlineStr">
         <is>
           <t>Verified from its own log. Strict 37/42, no lucky passes — ties gpt-5.6-luna and beats gpt-5.5 (36), but still below gpt-5.4 (42). Perfect on chains (20/20), fan-out (4/4), truncation (2/2) and at every hop depth above 2; all 5 losses are near-miss recovery (4/8) or refusal. Zero fabricated arguments, zero schema errors, zero tool errors, zero repeats across 142 calls. 327s.</t>
         </is>
@@ -3984,36 +4078,39 @@
         <v>0</v>
       </c>
       <c r="Z28" s="3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AA28" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AB28" s="3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AC28" s="3" t="n">
         <v>8</v>
       </c>
       <c r="AD28" s="3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE28" s="3" t="n">
         <v>10</v>
       </c>
       <c r="AF28" s="3" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AG28" s="3" t="n">
         <v>6</v>
       </c>
       <c r="AH28" s="3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="AJ28" s="1" t="inlineStr">
+      <c r="AJ28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK28" s="1" t="inlineStr">
         <is>
           <t>Verified from its own log. Strict 34/42 — the weakest of the three 5.6 variants (luna 37, sol 37) and below gpt-5.5 (36). Identical shape to its siblings: 20/20 chains, 4/4 fan-out, 2/2 truncation, perfect at hops 3-5, with every loss in near-miss recovery (2/8, the worst of the 5.x line) or refusal (6/8, 6 over-refusals). Zero fabricated arguments, zero schema errors, zero tool errors. Fastest of the pair at 210s and the leanest caller (2.95 calls/run).</t>
         </is>
@@ -4125,14 +4222,14 @@
     <row r="40">
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t>All rows recomputed from the regraded JSONL (grader deterministic-substring-v3). One transcription error found and corrected: ref /8 for qwen2.5:7b, 5 -&gt; 8.</t>
+          <t>Agent:NormaliseToolCallIds is now recorded per run (normalise_tool_call_ids). It was not before, which made it impossible to tell from the JSONL alone which runs had it on. Note that call_id_as_argument_count only detects the harness's own call_N shape, so it reads zero when normalisation is off regardless of what the model did.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t>v3 changes: fabricated arguments split into invented row id vs invented search term, and an answer truncated by the token cap can no longer be graded as a refusal. Regrading all 968 runs produced 0 correct/declined flips — both changes are additive.</t>
+          <t>Sch. Enum (column V) added: fabricated ids that walk a contiguous stretch of a range the tool advertises are now counted separately from invented ones. Regrading all runs moved 3 rows (qwen2.5:7b 18-&gt;8, qwen3.5:9b 34-&gt;2, qwen3.5:2b-q4_K_M 66-&gt;30) and produced 0 grade flips.</t>
         </is>
       </c>
     </row>

--- a/LlmMoveiAgentResults.xlsx
+++ b/LlmMoveiAgentResults.xlsx
@@ -7,7 +7,8 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="sql-shortcut control" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="sweep v2 (fixed)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="sql-shortcut control" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -75,7 +76,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -101,6 +102,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -201,6 +208,22 @@
     <comment ref="Z4" authorId="0" shapeId="0">
       <text>
         <t>Corrected by log validation. Was 5; runs-20260812-194621 records 8 of 8 decline cases correctly declined. Every other value in this row matched the log.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>log validation</author>
+  </authors>
+  <commentList>
+    <comment ref="I6" authorId="0" shapeId="0">
+      <text>
+        <t>The comparable figure across both groups: strict correct as a percentage of runs.
+Local n=2 (42 runs), hosted n=3 (63 runs), so raw counts are not comparable between them.</t>
       </text>
     </comment>
   </commentList>
@@ -4273,6 +4296,3476 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AJ35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="24" max="24"/>
+    <col width="7" customWidth="1" min="25" max="25"/>
+    <col width="8" customWidth="1" min="26" max="26"/>
+    <col width="70" customWidth="1" min="36" max="36"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>SWEEP v2 — re-run after two harness fixes. Output-format contract 1.2, not comparable with Sheet1 (1.1) on the refusal axis. (1) Ollama tool messages unwrapped so local models read the same result format hosted models always did. (2) The too-short-search-term rejection no longer ends 'you may retry with different arguments' on a goal that is unreachable — it now says the whole table is not listable and to say so. HOSTED MODELS RUN AT n=3 (63 runs), LOCAL AT n=2 (42), per concern 6 — compare Strict %, not raw counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>Tag Name</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>Output file</t>
+        </is>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Re-run?</t>
+        </is>
+      </c>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>Runs</t>
+        </is>
+      </c>
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
+        <is>
+          <t>Strict</t>
+        </is>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Strict %</t>
+        </is>
+      </c>
+      <c r="J6" s="14" t="inlineStr">
+        <is>
+          <t>Cap Hits</t>
+        </is>
+      </c>
+      <c r="K6" s="14" t="inlineStr">
+        <is>
+          <t>Errors</t>
+        </is>
+      </c>
+      <c r="L6" s="14" t="inlineStr">
+        <is>
+          <t>Emp. Ans</t>
+        </is>
+      </c>
+      <c r="M6" s="14" t="inlineStr">
+        <is>
+          <t>Avg TC p/r</t>
+        </is>
+      </c>
+      <c r="N6" s="14" t="inlineStr">
+        <is>
+          <t>Avg TC p/i</t>
+        </is>
+      </c>
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>Repeated</t>
+        </is>
+      </c>
+      <c r="P6" s="14" t="inlineStr">
+        <is>
+          <t>Tokens In</t>
+        </is>
+      </c>
+      <c r="Q6" s="14" t="inlineStr">
+        <is>
+          <t>Tokens Out</t>
+        </is>
+      </c>
+      <c r="R6" s="14" t="inlineStr">
+        <is>
+          <t>Fab. ID</t>
+        </is>
+      </c>
+      <c r="S6" s="14" t="inlineStr">
+        <is>
+          <t>Sch. Enum</t>
+        </is>
+      </c>
+      <c r="T6" s="14" t="inlineStr">
+        <is>
+          <t>Fab. Term</t>
+        </is>
+      </c>
+      <c r="U6" s="14" t="inlineStr">
+        <is>
+          <t>call id as arg</t>
+        </is>
+      </c>
+      <c r="V6" s="14" t="inlineStr">
+        <is>
+          <t>type m/m</t>
+        </is>
+      </c>
+      <c r="W6" s="14" t="inlineStr">
+        <is>
+          <t>schema err.</t>
+        </is>
+      </c>
+      <c r="X6" s="14" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="Y6" s="14" t="inlineStr">
+        <is>
+          <t>ref /N</t>
+        </is>
+      </c>
+      <c r="Z6" s="14" t="inlineStr">
+        <is>
+          <t>over-ref</t>
+        </is>
+      </c>
+      <c r="AA6" s="14" t="inlineStr">
+        <is>
+          <t>hop 2 ans</t>
+        </is>
+      </c>
+      <c r="AB6" s="14" t="inlineStr">
+        <is>
+          <t>hop 2 nav</t>
+        </is>
+      </c>
+      <c r="AC6" s="14" t="inlineStr">
+        <is>
+          <t>hop 3 ans</t>
+        </is>
+      </c>
+      <c r="AD6" s="14" t="inlineStr">
+        <is>
+          <t>hop 3 nav</t>
+        </is>
+      </c>
+      <c r="AE6" s="14" t="inlineStr">
+        <is>
+          <t>hop 4 ans</t>
+        </is>
+      </c>
+      <c r="AF6" s="14" t="inlineStr">
+        <is>
+          <t>hop 4 nav</t>
+        </is>
+      </c>
+      <c r="AG6" s="14" t="inlineStr">
+        <is>
+          <t>hop 5 ans</t>
+        </is>
+      </c>
+      <c r="AH6" s="14" t="inlineStr">
+        <is>
+          <t>hop 5 nav</t>
+        </is>
+      </c>
+      <c r="AI6" s="14" t="inlineStr">
+        <is>
+          <t>fmt</t>
+        </is>
+      </c>
+      <c r="AJ6" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Qwen2.5</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>1.5b</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>qwen2.5:1.5b</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-161413.jsonl</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>3258</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>245</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z7" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Qwen2.5</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>qwen2.5:3b</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-161527.jsonl</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>13</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="O8" s="3" t="n">
+        <v>106</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>8412</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>233</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="W8" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="X8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y8" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z8" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA8" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Qwen2.5</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>7b</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>qwen2.5:7b</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-161721.jsonl</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>9584</v>
+      </c>
+      <c r="Q9" s="3" t="n">
+        <v>123</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y9" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD9" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>4b-instruct</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>qwen3:4b-instruct</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-161942.jsonl</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>11143</v>
+      </c>
+      <c r="Q10" s="3" t="n">
+        <v>267</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3.5</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>4b</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>qwen3.5:4b</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-162237.jsonl</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O11" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="P11" s="3" t="n">
+        <v>16061</v>
+      </c>
+      <c r="Q11" s="3" t="n">
+        <v>218</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="U11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB11" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD11" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF11" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI11" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3.5</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>9b</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>qwen3.5:9b</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-162623.jsonl</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="O12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="3" t="n">
+        <v>15174</v>
+      </c>
+      <c r="Q12" s="3" t="n">
+        <v>278</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="U12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB12" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF12" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH12" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI12" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3.5</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>2b</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>qwen3.5:2b</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-163207.jsonl</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>47.6</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>18877</v>
+      </c>
+      <c r="Q13" s="3" t="n">
+        <v>372</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="U13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD13" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AJ13" s="15" t="inlineStr">
+        <is>
+          <t>Ollama default tag = Q8_0, 2.553 GB, digest 324d162b - NOT the same build as the row below; genuine quantisation pair, verified by ollama show. Unmoved by the fix (0.0pp) because it was never cap-bound. Its 0% on near-miss and fan-out is premature termination, not budget: 12 of 16 wrong answers never reached a required tool, 10 of those stopped at 4-6 calls against a cap of 10. Mean 4.18 calls per answerable run vs Q4_K_M 5.12 - the heavier build does less work. On fanout-store-cities it never calls get_city and supplies the city name from priors.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Qwen3.5</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>2b-q4_K_M</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>qwen3.5:2b-q4_K_M</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-163548.jsonl</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>20562</v>
+      </c>
+      <c r="Q14" s="3" t="n">
+        <v>418</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="U14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF14" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH14" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI14" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="AJ14" s="15" t="inlineStr">
+        <is>
+          <t>Q4_K_M, 1.812 GB, digest 124a03c3. Both builds scored strict 47.6% in v1; the 23.8pp gap opened entirely in v2. Q4 was the cap-bound one in v1 (16/42 cap hits, 7.43 calls per run) and the fix returned that budget (8 hits, 5.62 calls, +23.8pp); Q8 was never cap-bound and moved 0.0pp. Measures which build the harness defect was penalising, not which quantisation is better.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>LLama3.1</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>llama3.1</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-163917.jsonl</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>3103</v>
+      </c>
+      <c r="Q15" s="3" t="n">
+        <v>370</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>140</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y15" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD15" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>LLama3.2</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>3b</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>llama3.2</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-164421.jsonl</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>2820</v>
+      </c>
+      <c r="Q16" s="3" t="n">
+        <v>83</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="U16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y16" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Mistral-Nemo</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>12b</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>mistral-nemo:12b</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-164535.jsonl</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N17" s="3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="O17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="3" t="n">
+        <v>2490</v>
+      </c>
+      <c r="Q17" s="3" t="n">
+        <v>69</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X17" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y17" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z17" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Ministral</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>ministral-3</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-165049.jsonl</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="N18" s="3" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="O18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="3" t="n">
+        <v>8193</v>
+      </c>
+      <c r="Q18" s="3" t="n">
+        <v>99</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB18" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD18" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE18" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI18" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Gemma4</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>e2b</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>gemma4:e2b</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-165449.jsonl</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>66.7</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" s="3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="3" t="n">
+        <v>8049</v>
+      </c>
+      <c r="Q19" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z19" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD19" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF19" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Gemma4</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>e4b</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>gemma4:e4b</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-165618.jsonl</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>61.9</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" s="3" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="N20" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3" t="n">
+        <v>9349</v>
+      </c>
+      <c r="Q20" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AC20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD20" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF20" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH20" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI20" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>Hermes3</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>hermes3:8b</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-165821.jsonl</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N21" s="3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="O21" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="n">
+        <v>5765</v>
+      </c>
+      <c r="Q21" s="3" t="n">
+        <v>111</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="S21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y21" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>4o</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>gpt-4o</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-170007.jsonl</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>71.40000000000001</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="N22" s="3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="O22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3" t="n">
+        <v>7038</v>
+      </c>
+      <c r="Q22" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD22" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH22" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI22" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>4o-mini</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>gpt-4o-mini</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-171636.jsonl</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>63.5</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>7435</v>
+      </c>
+      <c r="Q23" s="3" t="n">
+        <v>96</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD23" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG23" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH23" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI23" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>5-4 std</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.4</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-172141.jsonl</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>8616</v>
+      </c>
+      <c r="Q24" s="3" t="n">
+        <v>100</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y24" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD24" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE24" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF24" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH24" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI24" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>5-5 std</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-172629.jsonl</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>8285</v>
+      </c>
+      <c r="Q25" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y25" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD25" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE25" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF25" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG25" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH25" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>5.6 luna</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.6-luna</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-173131.jsonl</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>8281</v>
+      </c>
+      <c r="Q26" s="3" t="n">
+        <v>90</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y26" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AC26" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD26" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE26" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF26" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH26" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI26" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>5.6 sol</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.6-sol</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-173653.jsonl</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>88.90000000000001</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>8225</v>
+      </c>
+      <c r="Q27" s="3" t="n">
+        <v>94</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y27" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AC27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD27" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE27" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF27" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH27" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>5.6 terra</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>gpt-5.6-terra</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-174314.jsonl</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>63</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>82.5</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N28" s="3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="O28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3" t="n">
+        <v>7431</v>
+      </c>
+      <c r="Q28" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="Y28" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z28" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA28" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AB28" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AC28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AD28" s="3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE28" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF28" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AG28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH28" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI28" s="3" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>NOT RE-RUN — zero tool calls in every recorded run, so neither fix can reach them. Figures below are the Sheet1 values at format 1.1, carried for completeness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Mistral</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>latest</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>mistral</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260814-122421.jsonl</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>no (0 calls)</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>2743</v>
+      </c>
+      <c r="Q31" s="3" t="n">
+        <v>212</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y31" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Granite3.3</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>granite3.3:8b</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260812-213730.jsonl</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>no (0 calls)</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>2559</v>
+      </c>
+      <c r="Q32" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y32" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Command R</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>7b</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>command-r7b</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260812-214520.jsonl</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>no (0 calls)</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>3452</v>
+      </c>
+      <c r="Q33" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y33" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Deepseek R1</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>8b</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>deepseek-r1:8b</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260812-221909.jsonl</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>no (0 calls)</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="M34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3" t="n">
+        <v>314</v>
+      </c>
+      <c r="Q34" s="3" t="n">
+        <v>2298</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Phi4</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>phi4-mini</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>runs-20260813-165949.jsonl</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>no (0 calls)</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v>21</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" s="3" t="n">
+        <v>2289</v>
+      </c>
+      <c r="Q35" s="3" t="n">
+        <v>113</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A30:AI30"/>
+    <mergeCell ref="A1:AI4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Q27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/LlmMoveiAgentResults.xlsx
+++ b/LlmMoveiAgentResults.xlsx
@@ -8233,7 +8233,7 @@
     <row r="1" ht="150" customHeight="1" s="16">
       <c r="A1" s="19" t="inlineStr">
         <is>
-          <t>SWEEP v3 - output-format contract 1.3 AND a changed system prompt, so this is not comparable with the v2 tab on any axis; the system_prompt_sha256 is recorded on every run. Three deliberate changes from v2: (1) a tool-call budget of 15 replaces the iteration cap as the work budget, because a model batching calls into one turn previously got an unbounded allowance while a serial model got 9 - 9 runs in v2 passed only because they batched past a budget that bound everyone else. (2) MaxIterations raised 10 -&gt; 20 so it guards runaway loops rather than acting as the budget; a serial model can now actually spend 15 calls and still answer. (3) The prompt no longer says 'call one tool at a time', which was an instruction most models ignored and which made the batching metric measure disobedience. ALSO: hop5-title-2025-renter was relabelled hop 4 (its requires_tools has only four groups; the year filter is reasoning, not a tool call) and a genuine 5-hop question, hop5-customer-country, was added. n=2 for LOCAL AND HOSTED alike, so raw counts are comparable across the two groups - but note hosted models are not deterministic and v2 ran them at n=3, so a hosted model moving by one run (2.3pp) cannot be told from a repeat flip. FINAL GRADES: deterministic-substring-v4; an explicitly labelled decline must complete its reachable evidence path.  ||  REGRADED 2026-08-16 under grader deterministic-substring-v5. The sweep was recorded under v3, whose refusal detection had no 'category' in its result nouns and no reach/provide/count in its inability verbs, so a decline of the form 'there is no Steampunk category in the database' matched nothing. Found by the grader unit tests, not by a sweep. Regrading recovered 20 correct declines across 11 models with NONE lost, and newly detected 2 genuine over-refusals. Pooled strict 57.9% -&gt; 60.0%, declines 66.7% -&gt; 78.2%, over-refusal 16.3% -&gt; 16.6%. A separate rule committed as v4 - requiring a decline to complete its evidence path - was REVERTED unapplied: it would have cost 14 correct declines across 8 models, nearly all for correctly saying the tools expose no director field. Raw records untouched; regraded copies are the .regraded.jsonl alongside.</t>
+          <t>SWEEP v3 - output-format contract 1.3 AND a changed system prompt, so this is not comparable with the v2 tab on any axis; the system_prompt_sha256 is recorded on every run. Three deliberate changes from v2: (1) a tool-call budget of 15 replaces the iteration cap as the work budget, because a model batching calls into one turn previously got an unbounded allowance while a serial model got 9 - 9 runs in v2 passed only because they batched past a budget that bound everyone else. (2) MaxIterations raised 10 -&gt; 20 so it guards runaway loops rather than acting as the budget; a serial model can now actually spend 15 calls and still answer. (3) The prompt no longer says 'call one tool at a time', which was an instruction most models ignored and which made the batching metric measure disobedience. ALSO: hop5-title-2025-renter was relabelled hop 4 (its requires_tools has only four groups; the year filter is reasoning, not a tool call) and a genuine 5-hop question, hop5-customer-country, was added. n=2 for LOCAL AND HOSTED alike, so raw counts are comparable across the two groups - but note hosted models are not deterministic and v2 ran them at n=3, so a hosted model moving by one run (2.3pp) cannot be told from a repeat flip. FINAL GRADES: deterministic-substring-v4; an explicitly labelled decline must complete its reachable evidence path.  ||  REGRADED 2026-08-16 under grader deterministic-substring-v5. The sweep was recorded under v3, whose refusal detection had no 'category' in its result nouns and no reach/provide/count in its inability verbs, so a decline of the form 'there is no Steampunk category in the database' matched nothing. Found by the grader unit tests, not by a sweep. Regrading recovered 20 correct declines across 11 models with NONE lost, and newly detected 2 genuine over-refusals. Pooled strict 57.9% -&gt; 60.0%, declines 66.7% -&gt; 78.2%, over-refusal 16.3% -&gt; 16.6%. A separate rule committed as v4 - requiring a decline to complete its evidence path - was REVERTED unapplied: it would have cost 14 correct declines across 8 models, nearly all for correctly saying the tools expose no director field. Raw records untouched; regraded copies are the .regraded.jsonl alongside.  ||  granite4.1:8b ADDED 2026-08-16, same configuration and prompt hash as the rest of the sweep. Its predecessor granite3.3:8b is one of the five zero-tool-call hard failures; 4.1 uses the tool channel correctly and places 13th of 23.</t>
         </is>
       </c>
     </row>
@@ -9908,22 +9908,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>gemma4</t>
+          <t>granite4.1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>e2b</t>
+          <t>8b</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>gemma4:e2b</t>
+          <t>granite4.1:8b</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>runs-20260815-162243.regraded.jsonl</t>
+          <t>runs-20260816-183434.regraded.jsonl</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -9933,13 +9933,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I20" t="n">
-        <v>65.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -9954,19 +9954,19 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.27</v>
+        <v>3.32</v>
       </c>
       <c r="O20" t="n">
         <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>397796</v>
+        <v>490757</v>
       </c>
       <c r="R20" t="n">
-        <v>3301</v>
+        <v>5358</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -9975,7 +9975,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -9987,13 +9987,13 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z20" t="n">
         <v>8</v>
       </c>
       <c r="AA20" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
@@ -10002,12 +10002,12 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12%</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
@@ -10034,22 +10034,22 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>qwen2.5</t>
+          <t>gemma4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7b</t>
+          <t>e2b</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>qwen2.5:7b</t>
+          <t>gemma4:e2b</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>runs-20260815-154137.regraded.jsonl</t>
+          <t>runs-20260815-162243.regraded.jsonl</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -10059,13 +10059,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H21" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I21" t="n">
-        <v>56.8</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -10080,22 +10080,22 @@
         <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.75</v>
+        <v>2.27</v>
       </c>
       <c r="O21" t="n">
         <v>1</v>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>428414</v>
+        <v>397796</v>
       </c>
       <c r="R21" t="n">
-        <v>5447</v>
+        <v>3301</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
@@ -10113,17 +10113,17 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Z21" t="n">
         <v>8</v>
       </c>
       <c r="AA21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -10160,7 +10160,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ministral-3</t>
+          <t>qwen2.5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10170,64 +10170,64 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ministral-3</t>
+          <t>qwen2.5:7b</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>runs-20260815-163317.regraded.jsonl</t>
+          <t>runs-20260815-154137.regraded.jsonl</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>27</v>
+      </c>
+      <c r="H22" t="n">
+        <v>25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>56.8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>24</v>
-      </c>
-      <c r="H22" t="n">
-        <v>24</v>
-      </c>
-      <c r="I22" t="n">
-        <v>55.8</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.13</v>
-      </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q22" t="n">
-        <v>356682</v>
+        <v>428414</v>
       </c>
       <c r="R22" t="n">
-        <v>5555</v>
+        <v>5447</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -10239,17 +10239,17 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Z22" t="n">
         <v>8</v>
       </c>
       <c r="AA22" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10259,12 +10259,12 @@
       </c>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -10286,7 +10286,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>qwen3.5</t>
+          <t>ministral-3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10296,64 +10296,64 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>qwen3.5:2b</t>
+          <t>ministral-3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>runs-20260815-162843.regraded.jsonl</t>
+          <t>runs-20260815-163317.regraded.jsonl</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>24</v>
+      </c>
+      <c r="H23" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" t="n">
+        <v>55.8</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="O23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>356682</v>
+      </c>
+      <c r="R23" t="n">
+        <v>5555</v>
+      </c>
+      <c r="S23" t="n">
         <v>2</v>
       </c>
-      <c r="G23" t="n">
-        <v>22</v>
-      </c>
-      <c r="H23" t="n">
-        <v>22</v>
-      </c>
-      <c r="I23" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>4</v>
-      </c>
-      <c r="K23" t="n">
-        <v>6</v>
-      </c>
-      <c r="L23" t="n">
-        <v>24</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="P23" t="n">
-        <v>76</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1044432</v>
-      </c>
-      <c r="R23" t="n">
-        <v>15736</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
       <c r="T23" t="n">
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -10362,20 +10362,20 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="Z23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AA23" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -10385,7 +10385,7 @@
       </c>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
@@ -10412,101 +10412,101 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>qwen2.5</t>
+          <t>qwen3.5</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3b</t>
+          <t>2b</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>qwen2.5:3b</t>
+          <t>qwen3.5:2b</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>runs-20260815-153855.regraded.jsonl</t>
+          <t>runs-20260815-162843.regraded.jsonl</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="H24" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>52.4</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="M24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>5.76</v>
       </c>
       <c r="O24" t="n">
-        <v>1.59</v>
+        <v>0.93</v>
       </c>
       <c r="P24" t="n">
-        <v>164</v>
+        <v>76</v>
       </c>
       <c r="Q24" t="n">
-        <v>395365</v>
+        <v>1044432</v>
       </c>
       <c r="R24" t="n">
-        <v>15126</v>
+        <v>15736</v>
       </c>
       <c r="S24" t="n">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="Y24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AA24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
@@ -10538,22 +10538,22 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>hermes3</t>
+          <t>qwen2.5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8b</t>
+          <t>3b</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hermes3:8b</t>
+          <t>qwen2.5:3b</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>runs-20260815-162622.regraded.jsonl</t>
+          <t>runs-20260815-153855.regraded.jsonl</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -10563,58 +10563,58 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I25" t="n">
-        <v>15.9</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
+        <v>111</v>
+      </c>
+      <c r="M25" t="n">
+        <v>8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="P25" t="n">
+        <v>164</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>395365</v>
+      </c>
+      <c r="R25" t="n">
+        <v>15126</v>
+      </c>
+      <c r="S25" t="n">
+        <v>169</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>4</v>
       </c>
-      <c r="M25" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="O25" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="P25" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>329636</v>
-      </c>
-      <c r="R25" t="n">
-        <v>5717</v>
-      </c>
-      <c r="S25" t="n">
-        <v>32</v>
-      </c>
-      <c r="T25" t="n">
-        <v>10</v>
-      </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
       <c r="V25" t="n">
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="Y25" t="n">
         <v>5</v>
@@ -10623,26 +10623,26 @@
         <v>8</v>
       </c>
       <c r="AA25" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
@@ -10664,22 +10664,22 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>mistral-nemo</t>
+          <t>hermes3</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>12b</t>
+          <t>8b</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>mistral-nemo:12b</t>
+          <t>hermes3:8b</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>runs-20260815-161301.regraded.jsonl</t>
+          <t>runs-20260815-162622.regraded.jsonl</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -10689,49 +10689,49 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" t="n">
-        <v>13.6</v>
+        <v>15.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.16</v>
+        <v>1.93</v>
       </c>
       <c r="O26" t="n">
-        <v>1.16</v>
+        <v>0.97</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q26" t="n">
-        <v>111212</v>
+        <v>329636</v>
       </c>
       <c r="R26" t="n">
-        <v>3054</v>
+        <v>5717</v>
       </c>
       <c r="S26" t="n">
+        <v>32</v>
+      </c>
+      <c r="T26" t="n">
         <v>10</v>
       </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -10740,20 +10740,20 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Z26" t="n">
         <v>8</v>
       </c>
       <c r="AA26" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -10790,17 +10790,22 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>llama3.2</t>
+          <t>mistral-nemo</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>12b</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>llama3.2</t>
+          <t>mistral-nemo:12b</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>runs-20260815-161152.regraded.jsonl</t>
+          <t>runs-20260815-161301.regraded.jsonl</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -10810,13 +10815,13 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>9.1</v>
+        <v>13.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -10831,46 +10836,46 @@
         <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="O27" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="P27" t="n">
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>126880</v>
+        <v>111212</v>
       </c>
       <c r="R27" t="n">
-        <v>3793</v>
+        <v>3054</v>
       </c>
       <c r="S27" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
         <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="Y27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z27" t="n">
         <v>8</v>
       </c>
       <c r="AA27" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
@@ -10911,17 +10916,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>llama3.1</t>
+          <t>llama3.2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>llama3.1</t>
+          <t>llama3.2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>runs-20260815-160815.regraded.jsonl</t>
+          <t>runs-20260815-161152.regraded.jsonl</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -10931,68 +10936,68 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>126880</v>
+      </c>
+      <c r="R28" t="n">
+        <v>3793</v>
+      </c>
+      <c r="S28" t="n">
+        <v>28</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>4</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>8</v>
+      </c>
+      <c r="X28" t="n">
+        <v>24</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA28" t="n">
         <v>6</v>
       </c>
-      <c r="H28" t="n">
-        <v>3</v>
-      </c>
-      <c r="I28" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>17</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="P28" t="n">
-        <v>38</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>135300</v>
-      </c>
-      <c r="R28" t="n">
-        <v>10728</v>
-      </c>
-      <c r="S28" t="n">
-        <v>109</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>10</v>
-      </c>
-      <c r="X28" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>11</v>
-      </c>
       <c r="AB28" t="inlineStr">
         <is>
           <t>0%</t>
@@ -11000,7 +11005,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr">
@@ -11032,7 +11037,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>qwen2.5</t>
+          <t>llama3.1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11042,12 +11047,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>qwen2.5:1.5b</t>
+          <t>llama3.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>runs-20260815-153758.regraded.jsonl</t>
+          <t>runs-20260815-160815.regraded.jsonl</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -11057,99 +11062,225 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
+        <v>6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
+        <v>17</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="P29" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>135300</v>
+      </c>
+      <c r="R29" t="n">
+        <v>10728</v>
+      </c>
+      <c r="S29" t="n">
+        <v>109</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>10</v>
+      </c>
+      <c r="X29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>b5525d200245</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>43e1f6be5097</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>qwen2.5</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1.5b</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>qwen2.5:1.5b</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>runs-20260815-153758.regraded.jsonl</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>44</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
         <v>4</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>4.5</v>
       </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" t="n">
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>5</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>0.34</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O30" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
         <v>145340</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>6886</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>6</v>
       </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
         <v>2</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y30" t="n">
         <v>2</v>
       </c>
-      <c r="Z29" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA29" t="n">
+      <c r="Z30" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA30" t="n">
         <v>2</v>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="AD29" t="inlineStr">
+      <c r="AD30" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AE29" t="inlineStr">
+      <c r="AE30" t="inlineStr">
         <is>
           <t>0%</t>
         </is>
       </c>
-      <c r="AF29" t="inlineStr">
+      <c r="AF30" t="inlineStr">
         <is>
           <t>1.3</t>
         </is>
       </c>
-      <c r="AG29" t="inlineStr">
+      <c r="AG30" t="inlineStr">
         <is>
           <t>b5525d200245</t>
         </is>
       </c>
-      <c r="AH29" t="inlineStr">
+      <c r="AH30" t="inlineStr">
         <is>
           <t>43e1f6be5097</t>
         </is>
